--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7C114C-FEE2-487D-89A9-4A019681F86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C89F306-245C-4853-9B0D-6ACB1400E9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,9 +18,9 @@
     <sheet name="Gesamt" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Ausgaben!$B$2:$J$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Ausgaben!$B$2:$J$173</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Einnahmen!$A$2:$H$106</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Ausgaben!$A$1:$I$175</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Ausgaben!$A$1:$I$177</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Einnahmen!$A$1:$H$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="75">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -229,6 +229,36 @@
   </si>
   <si>
     <t>Helferessen</t>
+  </si>
+  <si>
+    <t>SPD Miete 11.2.</t>
+  </si>
+  <si>
+    <t>Spende B.Schmäschke</t>
+  </si>
+  <si>
+    <t>B.Schmäschke Miete</t>
+  </si>
+  <si>
+    <t>Trauerkarte Laich</t>
+  </si>
+  <si>
+    <t>Strato Webservice</t>
+  </si>
+  <si>
+    <t>Porto JHV</t>
+  </si>
+  <si>
+    <t>Richter Druck, Weltfrauentag</t>
+  </si>
+  <si>
+    <t>Porto Weltfrauentag</t>
+  </si>
+  <si>
+    <t>16a</t>
+  </si>
+  <si>
+    <t>16b</t>
   </si>
 </sst>
 </file>
@@ -896,7 +926,17 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="49">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1282,7 +1322,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bernd Wild" refreshedDate="45318.474550578707" createdVersion="4" refreshedVersion="8" minRefreshableVersion="3" recordCount="168" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="E2:I171" sheet="Ausgaben"/>
+    <worksheetSource ref="E2:I173" sheet="Ausgaben"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="Zweck II" numFmtId="0">
@@ -3672,17 +3712,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="43">
+    <format dxfId="45">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3786,17 +3826,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="46">
+    <format dxfId="48">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="46">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4992,9 +5032,15 @@
       <c r="E3" s="12">
         <v>0</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="F3" s="26">
+        <v>583.69000000002416</v>
+      </c>
+      <c r="G3" s="26">
+        <v>2000.5</v>
+      </c>
+      <c r="H3" s="26">
+        <v>4050.9699999999989</v>
+      </c>
       <c r="I3" s="2"/>
       <c r="J3" s="3" t="s">
         <v>13</v>
@@ -5154,7 +5200,9 @@
       <c r="C10" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
       <c r="G10" s="17"/>
@@ -5167,160 +5215,180 @@
       </c>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
+      <c r="A11" s="14">
+        <v>46069</v>
+      </c>
       <c r="B11" s="48">
         <v>8</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="18"/>
+      <c r="C11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E11" s="19"/>
       <c r="F11" s="20"/>
       <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
+      <c r="H11" s="17">
+        <v>20</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
+      <c r="A12" s="14">
+        <v>46071</v>
+      </c>
       <c r="B12" s="48">
         <v>9</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E12" s="19"/>
       <c r="F12" s="20"/>
       <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
+      <c r="H12" s="17">
+        <v>12</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
+      <c r="A13" s="14">
+        <v>46076</v>
+      </c>
       <c r="B13" s="48">
         <v>10</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="18"/>
+      <c r="C13" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E13" s="19"/>
       <c r="F13" s="20"/>
       <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
+      <c r="H13" s="17">
+        <v>107</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
+      <c r="A14" s="14">
+        <v>46083</v>
+      </c>
       <c r="B14" s="48">
         <v>11</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
+      <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
       <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
+      <c r="H14" s="17">
+        <v>20</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
+      <c r="A15" s="14">
+        <v>46083</v>
+      </c>
       <c r="B15" s="48">
         <v>12</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="18"/>
+      <c r="C15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E15" s="19"/>
       <c r="F15" s="20"/>
       <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
+      <c r="H15" s="17">
+        <v>50</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
+      <c r="A16" s="14">
+        <v>46090</v>
+      </c>
       <c r="B16" s="48">
         <v>13</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="18"/>
+      <c r="C16" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E16" s="19"/>
       <c r="F16" s="20"/>
       <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
+      <c r="H16" s="17">
+        <v>105</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
       <c r="B17" s="48">
         <v>14</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
       <c r="B18" s="48">
         <v>15</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
       <c r="B19" s="48">
         <v>16</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
       <c r="B20" s="48">
         <v>17</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
@@ -6579,15 +6647,15 @@
       </c>
       <c r="F110" s="26">
         <f>SUM(F3:F109)</f>
-        <v>4126.1000000000004</v>
+        <v>4709.7900000000245</v>
       </c>
       <c r="G110" s="26">
         <f>SUM(G3:G109)</f>
-        <v>0</v>
+        <v>2000.5</v>
       </c>
       <c r="H110" s="26">
         <f>SUM(H3:H109)</f>
-        <v>269</v>
+        <v>4633.9699999999993</v>
       </c>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
@@ -6612,20 +6680,20 @@
       <c r="C112" s="23"/>
       <c r="D112" s="45"/>
       <c r="E112" s="26">
-        <f>E110+Ausgaben!F176</f>
+        <f>E110+Ausgaben!F178</f>
         <v>0</v>
       </c>
       <c r="F112" s="26">
-        <f>F110+Ausgaben!G176</f>
-        <v>2333.9500000000003</v>
+        <f>F110+Ausgaben!G178</f>
+        <v>2381.1300000000247</v>
       </c>
       <c r="G112" s="26">
-        <f>G110+Ausgaben!H176</f>
-        <v>0</v>
+        <f>G110+Ausgaben!H178</f>
+        <v>2000.5</v>
       </c>
       <c r="H112" s="26">
-        <f>H110+Ausgaben!I176</f>
-        <v>-2894.41</v>
+        <f>H110+Ausgaben!I178</f>
+        <v>1448.0599999999995</v>
       </c>
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
@@ -6650,7 +6718,7 @@
       <c r="C114" s="22"/>
       <c r="D114" s="27">
         <f>SUM(E112:H112)</f>
-        <v>-560.45999999999958</v>
+        <v>5829.6900000000242</v>
       </c>
       <c r="E114" s="16"/>
       <c r="F114" s="17"/>
@@ -7389,118 +7457,118 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B82">
-    <cfRule type="cellIs" dxfId="40" priority="197" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="B82 H4:H10 G11:H16">
+    <cfRule type="cellIs" dxfId="42" priority="198" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C98:D99">
-    <cfRule type="cellIs" dxfId="39" priority="50" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="51" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:D88">
-    <cfRule type="cellIs" dxfId="38" priority="14" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="15" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:F81">
-    <cfRule type="cellIs" dxfId="37" priority="15" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="16" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D77:G80">
-    <cfRule type="cellIs" dxfId="36" priority="16" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D100:G109">
-    <cfRule type="cellIs" dxfId="35" priority="48" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="49" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="cellIs" dxfId="34" priority="75" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="76" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40:F41">
-    <cfRule type="cellIs" dxfId="33" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="14" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E45:F45">
-    <cfRule type="cellIs" dxfId="32" priority="35" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E14:G14">
-    <cfRule type="cellIs" dxfId="31" priority="285" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="36" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:G39 G40:G46">
-    <cfRule type="cellIs" dxfId="30" priority="37" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="38" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47:G48 G49:G50 E50:F50 F51:G51 G52:G57">
-    <cfRule type="cellIs" dxfId="29" priority="95" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="96" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E68:G70 G81:G82">
-    <cfRule type="cellIs" dxfId="28" priority="69" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="70" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E83:G88 D89:G97">
-    <cfRule type="cellIs" dxfId="27" priority="51" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="52" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:H3 G98 E99:G99 D109:H109 E110:H174 D114">
-    <cfRule type="cellIs" dxfId="26" priority="349" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E3 G98 E99:G99 D109:H109 E110:H174 D114">
+    <cfRule type="cellIs" dxfId="29" priority="350" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24:G24">
-    <cfRule type="cellIs" dxfId="25" priority="270" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="271" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58:G59">
-    <cfRule type="cellIs" dxfId="24" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F71:G71">
-    <cfRule type="cellIs" dxfId="23" priority="67" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="68" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A92:C92">
-    <cfRule type="cellIs" dxfId="22" priority="183" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="184" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G25:G26">
-    <cfRule type="cellIs" dxfId="21" priority="267" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="268" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27:H32">
-    <cfRule type="cellIs" dxfId="20" priority="44" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="45" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6 G15:G23 H33:H109 E53:F57 D60:G67 D68:D76 E72:G76 A93:A96 D8:D60 H4:H26">
-    <cfRule type="cellIs" dxfId="19" priority="55" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G21:G23 H21:H26 D21:D60 H33:H109 E53:F57 D60:G67 D68:D76 E72:G76 A93:A96">
+    <cfRule type="cellIs" dxfId="22" priority="56" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:H3">
+    <cfRule type="cellIs" dxfId="21" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D109" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D21:D109" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$J$1:$J$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -7521,7 +7589,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:IL242"/>
+  <dimension ref="A1:IL244"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="43" customWidth="1"/>
@@ -8007,20 +8075,20 @@
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="41"/>
       <c r="B19" s="14">
-        <v>46057</v>
-      </c>
-      <c r="C19" s="48">
-        <v>17</v>
+        <v>46056</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>73</v>
       </c>
       <c r="D19" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>20</v>
+        <v>51</v>
+      </c>
+      <c r="E19" s="82" t="s">
+        <v>21</v>
       </c>
       <c r="F19" s="19"/>
       <c r="G19" s="20">
-        <v>-12</v>
+        <v>-112</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
@@ -8033,20 +8101,20 @@
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="41"/>
       <c r="B20" s="14">
-        <v>45694</v>
-      </c>
-      <c r="C20" s="48">
-        <v>18</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>22</v>
+        <v>46056</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="82" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="19"/>
       <c r="G20" s="20">
-        <v>-46.5</v>
+        <v>-52</v>
       </c>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
@@ -8057,20 +8125,20 @@
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="41"/>
       <c r="B21" s="14">
-        <v>46062</v>
+        <v>46057</v>
       </c>
       <c r="C21" s="48">
-        <v>19</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="82" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="D21" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F21" s="19"/>
       <c r="G21" s="20">
-        <v>-76.989999999999995</v>
+        <v>-12</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
@@ -8081,20 +8149,20 @@
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="41"/>
       <c r="B22" s="14">
-        <v>46062</v>
+        <v>45694</v>
       </c>
       <c r="C22" s="48">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>13</v>
+        <v>61</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F22" s="19"/>
       <c r="G22" s="20">
-        <v>-113.05</v>
+        <v>-46.5</v>
       </c>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
@@ -8108,17 +8176,17 @@
         <v>46062</v>
       </c>
       <c r="C23" s="48">
+        <v>19</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="82" t="s">
         <v>21</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="F23" s="19"/>
       <c r="G23" s="20">
-        <v>-96</v>
+        <v>-76.989999999999995</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
@@ -8128,14 +8196,22 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="41"/>
-      <c r="B24" s="14"/>
+      <c r="B24" s="14">
+        <v>46062</v>
+      </c>
       <c r="C24" s="48">
-        <v>22</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="82"/>
+        <v>20</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
+      <c r="G24" s="20">
+        <v>-113.05</v>
+      </c>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
       <c r="J24" s="4"/>
@@ -8144,14 +8220,22 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="41"/>
-      <c r="B25" s="14"/>
+      <c r="B25" s="14">
+        <v>46062</v>
+      </c>
       <c r="C25" s="48">
-        <v>23</v>
-      </c>
-      <c r="D25" s="81"/>
-      <c r="E25" s="82"/>
+        <v>21</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
+      <c r="G25" s="20">
+        <v>-96</v>
+      </c>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
       <c r="J25" s="4"/>
@@ -8160,14 +8244,22 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="41"/>
-      <c r="B26" s="14"/>
+      <c r="B26" s="14">
+        <v>46063</v>
+      </c>
       <c r="C26" s="48">
-        <v>24</v>
-      </c>
-      <c r="D26" s="81"/>
-      <c r="E26" s="82"/>
+        <v>22</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="F26" s="19"/>
-      <c r="G26" s="20"/>
+      <c r="G26" s="20">
+        <v>-20</v>
+      </c>
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
       <c r="J26" s="4"/>
@@ -8176,14 +8268,22 @@
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="41"/>
-      <c r="B27" s="14"/>
+      <c r="B27" s="14">
+        <v>46065</v>
+      </c>
       <c r="C27" s="48">
-        <v>25</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="82"/>
+        <v>23</v>
+      </c>
+      <c r="D27" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F27" s="19"/>
-      <c r="G27" s="20"/>
+      <c r="G27" s="20">
+        <v>-12.98</v>
+      </c>
       <c r="H27" s="20"/>
       <c r="I27" s="20"/>
       <c r="J27" s="4"/>
@@ -8192,14 +8292,22 @@
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="41"/>
-      <c r="B28" s="14"/>
+      <c r="B28" s="14">
+        <v>46069</v>
+      </c>
       <c r="C28" s="48">
-        <v>26</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="82"/>
+        <v>24</v>
+      </c>
+      <c r="D28" s="81" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F28" s="19"/>
-      <c r="G28" s="20"/>
+      <c r="G28" s="20">
+        <v>-20</v>
+      </c>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
       <c r="J28" s="4"/>
@@ -8208,30 +8316,46 @@
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="41"/>
-      <c r="B29" s="14"/>
+      <c r="B29" s="14">
+        <v>46070</v>
+      </c>
       <c r="C29" s="48">
-        <v>27</v>
-      </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="21"/>
+        <v>25</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F29" s="19"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
+      <c r="I29" s="20">
+        <v>-22.5</v>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="41"/>
-      <c r="B30" s="14"/>
+      <c r="B30" s="14">
+        <v>46071</v>
+      </c>
       <c r="C30" s="48">
-        <v>28</v>
-      </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="21"/>
+        <v>26</v>
+      </c>
+      <c r="D30" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F30" s="19"/>
-      <c r="G30" s="20"/>
+      <c r="G30" s="20">
+        <v>-19.34</v>
+      </c>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
       <c r="J30" s="4"/>
@@ -8240,14 +8364,22 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="41"/>
-      <c r="B31" s="14"/>
+      <c r="B31" s="14">
+        <v>46072</v>
+      </c>
       <c r="C31" s="48">
-        <v>29</v>
-      </c>
-      <c r="D31" s="81"/>
-      <c r="E31" s="82"/>
+        <v>27</v>
+      </c>
+      <c r="D31" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F31" s="19"/>
-      <c r="G31" s="20"/>
+      <c r="G31" s="20">
+        <v>-28.7</v>
+      </c>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
       <c r="J31" s="4"/>
@@ -8256,30 +8388,44 @@
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="41"/>
-      <c r="B32" s="14"/>
+      <c r="B32" s="14">
+        <v>46072</v>
+      </c>
       <c r="C32" s="48">
-        <v>30</v>
-      </c>
-      <c r="D32" s="81"/>
-      <c r="E32" s="21"/>
+        <v>28</v>
+      </c>
+      <c r="D32" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F32" s="19"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
+      <c r="G32" s="20">
+        <v>-16.010000000000002</v>
+      </c>
       <c r="J32" s="4"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="41"/>
-      <c r="B33" s="14"/>
+      <c r="B33" s="14">
+        <v>46076</v>
+      </c>
       <c r="C33" s="48">
-        <v>31</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" s="82"/>
+        <v>29</v>
+      </c>
+      <c r="D33" s="81" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="82" t="s">
+        <v>14</v>
+      </c>
       <c r="F33" s="19"/>
-      <c r="G33" s="20"/>
+      <c r="G33" s="20">
+        <v>-19</v>
+      </c>
       <c r="H33" s="20"/>
       <c r="I33" s="20"/>
       <c r="J33" s="4"/>
@@ -8288,14 +8434,22 @@
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="41"/>
-      <c r="B34" s="14"/>
+      <c r="B34" s="14">
+        <v>46076</v>
+      </c>
       <c r="C34" s="48">
-        <v>32</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="82"/>
+        <v>30</v>
+      </c>
+      <c r="D34" s="81" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F34" s="19"/>
-      <c r="G34" s="20"/>
+      <c r="G34" s="20">
+        <v>-69.86</v>
+      </c>
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
       <c r="J34" s="4"/>
@@ -8304,14 +8458,22 @@
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="41"/>
-      <c r="B35" s="14"/>
+      <c r="B35" s="14">
+        <v>46078</v>
+      </c>
       <c r="C35" s="48">
-        <v>33</v>
-      </c>
-      <c r="D35" s="81"/>
-      <c r="E35" s="82"/>
+        <v>31</v>
+      </c>
+      <c r="D35" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F35" s="19"/>
-      <c r="G35" s="20"/>
+      <c r="G35" s="20">
+        <v>-4.99</v>
+      </c>
       <c r="H35" s="20"/>
       <c r="I35" s="20"/>
       <c r="J35" s="4"/>
@@ -8320,14 +8482,22 @@
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="41"/>
-      <c r="B36" s="14"/>
+      <c r="B36" s="14">
+        <v>46084</v>
+      </c>
       <c r="C36" s="48">
-        <v>34</v>
-      </c>
-      <c r="D36" s="81"/>
-      <c r="E36" s="82"/>
+        <v>32</v>
+      </c>
+      <c r="D36" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F36" s="19"/>
-      <c r="G36" s="20"/>
+      <c r="G36" s="20">
+        <v>-38.520000000000003</v>
+      </c>
       <c r="H36" s="20"/>
       <c r="I36" s="20"/>
       <c r="J36" s="4"/>
@@ -8336,14 +8506,22 @@
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="41"/>
-      <c r="B37" s="14"/>
+      <c r="B37" s="14">
+        <v>46084</v>
+      </c>
       <c r="C37" s="48">
-        <v>35</v>
-      </c>
-      <c r="D37" s="3"/>
-      <c r="E37" s="82"/>
+        <v>33</v>
+      </c>
+      <c r="D37" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F37" s="19"/>
-      <c r="G37" s="20"/>
+      <c r="G37" s="20">
+        <v>-32.450000000000003</v>
+      </c>
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
       <c r="J37" s="4"/>
@@ -8352,14 +8530,22 @@
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="41"/>
-      <c r="B38" s="14"/>
+      <c r="B38" s="14">
+        <v>46085</v>
+      </c>
       <c r="C38" s="48">
-        <v>36</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="82"/>
+        <v>34</v>
+      </c>
+      <c r="D38" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="F38" s="19"/>
-      <c r="G38" s="20"/>
+      <c r="G38" s="20">
+        <v>-12</v>
+      </c>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
       <c r="J38" s="4"/>
@@ -8368,14 +8554,22 @@
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="41"/>
-      <c r="B39" s="14"/>
+      <c r="B39" s="14">
+        <v>46085</v>
+      </c>
       <c r="C39" s="48">
-        <v>37</v>
-      </c>
-      <c r="D39" s="3"/>
-      <c r="E39" s="82"/>
+        <v>35</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F39" s="19"/>
-      <c r="G39" s="20"/>
+      <c r="G39" s="20">
+        <v>-12.16</v>
+      </c>
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
       <c r="J39" s="4"/>
@@ -8384,14 +8578,22 @@
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="41"/>
-      <c r="B40" s="14"/>
+      <c r="B40" s="14">
+        <v>46090</v>
+      </c>
       <c r="C40" s="48">
-        <v>38</v>
-      </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="82"/>
+        <v>36</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F40" s="19"/>
-      <c r="G40" s="20"/>
+      <c r="G40" s="20">
+        <v>-66.5</v>
+      </c>
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
       <c r="J40" s="4"/>
@@ -8402,7 +8604,7 @@
       <c r="A41" s="41"/>
       <c r="B41" s="14"/>
       <c r="C41" s="48">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="82"/>
@@ -8418,7 +8620,7 @@
       <c r="A42" s="41"/>
       <c r="B42" s="14"/>
       <c r="C42" s="48">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="82"/>
@@ -8434,7 +8636,7 @@
       <c r="A43" s="41"/>
       <c r="B43" s="14"/>
       <c r="C43" s="48">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="82"/>
@@ -8450,7 +8652,7 @@
       <c r="A44" s="41"/>
       <c r="B44" s="14"/>
       <c r="C44" s="48">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="82"/>
@@ -8466,7 +8668,7 @@
       <c r="A45" s="41"/>
       <c r="B45" s="14"/>
       <c r="C45" s="48">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="82"/>
@@ -8482,9 +8684,9 @@
       <c r="A46" s="41"/>
       <c r="B46" s="14"/>
       <c r="C46" s="48">
-        <v>44</v>
-      </c>
-      <c r="D46" s="81"/>
+        <v>42</v>
+      </c>
+      <c r="D46" s="3"/>
       <c r="E46" s="82"/>
       <c r="F46" s="19"/>
       <c r="G46" s="20"/>
@@ -8498,7 +8700,7 @@
       <c r="A47" s="41"/>
       <c r="B47" s="14"/>
       <c r="C47" s="48">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="82"/>
@@ -8514,9 +8716,9 @@
       <c r="A48" s="41"/>
       <c r="B48" s="14"/>
       <c r="C48" s="48">
-        <v>46</v>
-      </c>
-      <c r="D48" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="D48" s="81"/>
       <c r="E48" s="82"/>
       <c r="F48" s="19"/>
       <c r="G48" s="20"/>
@@ -8530,7 +8732,7 @@
       <c r="A49" s="41"/>
       <c r="B49" s="14"/>
       <c r="C49" s="48">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="82"/>
@@ -8546,7 +8748,7 @@
       <c r="A50" s="41"/>
       <c r="B50" s="14"/>
       <c r="C50" s="48">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="82"/>
@@ -8562,7 +8764,7 @@
       <c r="A51" s="41"/>
       <c r="B51" s="14"/>
       <c r="C51" s="48">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="82"/>
@@ -8578,10 +8780,10 @@
       <c r="A52" s="41"/>
       <c r="B52" s="14"/>
       <c r="C52" s="48">
-        <v>50</v>
-      </c>
-      <c r="D52" s="37"/>
-      <c r="E52" s="18"/>
+        <v>48</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="82"/>
       <c r="F52" s="19"/>
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
@@ -8594,7 +8796,7 @@
       <c r="A53" s="41"/>
       <c r="B53" s="14"/>
       <c r="C53" s="48">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="82"/>
@@ -8610,10 +8812,10 @@
       <c r="A54" s="41"/>
       <c r="B54" s="14"/>
       <c r="C54" s="48">
-        <v>52</v>
-      </c>
-      <c r="D54" s="3"/>
-      <c r="E54" s="21"/>
+        <v>50</v>
+      </c>
+      <c r="D54" s="37"/>
+      <c r="E54" s="18"/>
       <c r="F54" s="19"/>
       <c r="G54" s="20"/>
       <c r="H54" s="20"/>
@@ -8626,7 +8828,7 @@
       <c r="A55" s="41"/>
       <c r="B55" s="14"/>
       <c r="C55" s="48">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="82"/>
@@ -8642,10 +8844,10 @@
       <c r="A56" s="41"/>
       <c r="B56" s="14"/>
       <c r="C56" s="48">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D56" s="3"/>
-      <c r="E56" s="82"/>
+      <c r="E56" s="21"/>
       <c r="F56" s="19"/>
       <c r="G56" s="20"/>
       <c r="H56" s="20"/>
@@ -8658,7 +8860,7 @@
       <c r="A57" s="41"/>
       <c r="B57" s="14"/>
       <c r="C57" s="48">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="82"/>
@@ -8674,7 +8876,7 @@
       <c r="A58" s="41"/>
       <c r="B58" s="14"/>
       <c r="C58" s="48">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="82"/>
@@ -8690,9 +8892,9 @@
       <c r="A59" s="41"/>
       <c r="B59" s="14"/>
       <c r="C59" s="48">
-        <v>57</v>
-      </c>
-      <c r="D59" s="81"/>
+        <v>55</v>
+      </c>
+      <c r="D59" s="3"/>
       <c r="E59" s="82"/>
       <c r="F59" s="19"/>
       <c r="G59" s="20"/>
@@ -8706,7 +8908,7 @@
       <c r="A60" s="41"/>
       <c r="B60" s="14"/>
       <c r="C60" s="48">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="82"/>
@@ -8722,9 +8924,9 @@
       <c r="A61" s="41"/>
       <c r="B61" s="14"/>
       <c r="C61" s="48">
-        <v>59</v>
-      </c>
-      <c r="D61" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="D61" s="81"/>
       <c r="E61" s="82"/>
       <c r="F61" s="19"/>
       <c r="G61" s="20"/>
@@ -8738,11 +8940,11 @@
       <c r="A62" s="41"/>
       <c r="B62" s="14"/>
       <c r="C62" s="48">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="82"/>
-      <c r="F62" s="16"/>
+      <c r="F62" s="19"/>
       <c r="G62" s="20"/>
       <c r="H62" s="20"/>
       <c r="I62" s="20"/>
@@ -8754,11 +8956,11 @@
       <c r="A63" s="41"/>
       <c r="B63" s="14"/>
       <c r="C63" s="48">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="82"/>
-      <c r="F63" s="16"/>
+      <c r="F63" s="19"/>
       <c r="G63" s="20"/>
       <c r="H63" s="20"/>
       <c r="I63" s="20"/>
@@ -8770,11 +8972,11 @@
       <c r="A64" s="41"/>
       <c r="B64" s="14"/>
       <c r="C64" s="48">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="82"/>
-      <c r="F64" s="19"/>
+      <c r="F64" s="16"/>
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
       <c r="I64" s="20"/>
@@ -8786,11 +8988,11 @@
       <c r="A65" s="41"/>
       <c r="B65" s="14"/>
       <c r="C65" s="48">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D65" s="3"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="19"/>
+      <c r="E65" s="82"/>
+      <c r="F65" s="16"/>
       <c r="G65" s="20"/>
       <c r="H65" s="20"/>
       <c r="I65" s="20"/>
@@ -8802,11 +9004,11 @@
       <c r="A66" s="41"/>
       <c r="B66" s="14"/>
       <c r="C66" s="48">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="82"/>
-      <c r="F66" s="16"/>
+      <c r="F66" s="19"/>
       <c r="G66" s="20"/>
       <c r="H66" s="20"/>
       <c r="I66" s="20"/>
@@ -8818,11 +9020,11 @@
       <c r="A67" s="41"/>
       <c r="B67" s="14"/>
       <c r="C67" s="48">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D67" s="3"/>
-      <c r="E67" s="82"/>
-      <c r="F67" s="16"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="19"/>
       <c r="G67" s="20"/>
       <c r="H67" s="20"/>
       <c r="I67" s="20"/>
@@ -8834,12 +9036,12 @@
       <c r="A68" s="41"/>
       <c r="B68" s="14"/>
       <c r="C68" s="48">
-        <v>66</v>
-      </c>
-      <c r="D68" s="81"/>
+        <v>64</v>
+      </c>
+      <c r="D68" s="3"/>
       <c r="E68" s="82"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="20"/>
       <c r="H68" s="20"/>
       <c r="I68" s="20"/>
       <c r="J68" s="4"/>
@@ -8850,11 +9052,11 @@
       <c r="A69" s="41"/>
       <c r="B69" s="14"/>
       <c r="C69" s="48">
-        <v>67</v>
-      </c>
-      <c r="D69" s="81"/>
+        <v>65</v>
+      </c>
+      <c r="D69" s="3"/>
       <c r="E69" s="82"/>
-      <c r="F69" s="19"/>
+      <c r="F69" s="16"/>
       <c r="G69" s="20"/>
       <c r="H69" s="20"/>
       <c r="I69" s="20"/>
@@ -8866,12 +9068,12 @@
       <c r="A70" s="41"/>
       <c r="B70" s="14"/>
       <c r="C70" s="48">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D70" s="81"/>
       <c r="E70" s="82"/>
       <c r="F70" s="19"/>
-      <c r="G70" s="20"/>
+      <c r="G70" s="19"/>
       <c r="H70" s="20"/>
       <c r="I70" s="20"/>
       <c r="J70" s="4"/>
@@ -8882,13 +9084,13 @@
       <c r="A71" s="41"/>
       <c r="B71" s="14"/>
       <c r="C71" s="48">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D71" s="81"/>
       <c r="E71" s="82"/>
       <c r="F71" s="19"/>
       <c r="G71" s="20"/>
-      <c r="H71" s="19"/>
+      <c r="H71" s="20"/>
       <c r="I71" s="20"/>
       <c r="J71" s="4"/>
       <c r="K71" s="2"/>
@@ -8898,9 +9100,9 @@
       <c r="A72" s="41"/>
       <c r="B72" s="14"/>
       <c r="C72" s="48">
-        <v>70</v>
-      </c>
-      <c r="D72" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="D72" s="81"/>
       <c r="E72" s="82"/>
       <c r="F72" s="19"/>
       <c r="G72" s="20"/>
@@ -8914,13 +9116,13 @@
       <c r="A73" s="41"/>
       <c r="B73" s="14"/>
       <c r="C73" s="48">
-        <v>71</v>
-      </c>
-      <c r="D73" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="D73" s="81"/>
       <c r="E73" s="82"/>
       <c r="F73" s="19"/>
       <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
+      <c r="H73" s="19"/>
       <c r="I73" s="20"/>
       <c r="J73" s="4"/>
       <c r="K73" s="2"/>
@@ -8930,7 +9132,7 @@
       <c r="A74" s="41"/>
       <c r="B74" s="14"/>
       <c r="C74" s="48">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="82"/>
@@ -8946,7 +9148,7 @@
       <c r="A75" s="41"/>
       <c r="B75" s="14"/>
       <c r="C75" s="48">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="82"/>
@@ -8962,7 +9164,7 @@
       <c r="A76" s="41"/>
       <c r="B76" s="14"/>
       <c r="C76" s="48">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="82"/>
@@ -8978,7 +9180,7 @@
       <c r="A77" s="41"/>
       <c r="B77" s="14"/>
       <c r="C77" s="48">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="82"/>
@@ -8994,7 +9196,7 @@
       <c r="A78" s="41"/>
       <c r="B78" s="14"/>
       <c r="C78" s="48">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="82"/>
@@ -9010,7 +9212,7 @@
       <c r="A79" s="41"/>
       <c r="B79" s="14"/>
       <c r="C79" s="48">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="82"/>
@@ -9026,7 +9228,7 @@
       <c r="A80" s="41"/>
       <c r="B80" s="14"/>
       <c r="C80" s="48">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="82"/>
@@ -9042,7 +9244,7 @@
       <c r="A81" s="41"/>
       <c r="B81" s="14"/>
       <c r="C81" s="48">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="82"/>
@@ -9058,7 +9260,7 @@
       <c r="A82" s="41"/>
       <c r="B82" s="14"/>
       <c r="C82" s="48">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="82"/>
@@ -9074,7 +9276,7 @@
       <c r="A83" s="41"/>
       <c r="B83" s="14"/>
       <c r="C83" s="48">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="82"/>
@@ -9090,9 +9292,9 @@
       <c r="A84" s="41"/>
       <c r="B84" s="14"/>
       <c r="C84" s="48">
-        <v>82</v>
-      </c>
-      <c r="D84" s="81"/>
+        <v>80</v>
+      </c>
+      <c r="D84" s="3"/>
       <c r="E84" s="82"/>
       <c r="F84" s="19"/>
       <c r="G84" s="20"/>
@@ -9106,9 +9308,9 @@
       <c r="A85" s="41"/>
       <c r="B85" s="14"/>
       <c r="C85" s="48">
-        <v>83</v>
-      </c>
-      <c r="D85" s="81"/>
+        <v>81</v>
+      </c>
+      <c r="D85" s="3"/>
       <c r="E85" s="82"/>
       <c r="F85" s="19"/>
       <c r="G85" s="20"/>
@@ -9122,7 +9324,7 @@
       <c r="A86" s="41"/>
       <c r="B86" s="14"/>
       <c r="C86" s="48">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D86" s="81"/>
       <c r="E86" s="82"/>
@@ -9138,9 +9340,9 @@
       <c r="A87" s="41"/>
       <c r="B87" s="14"/>
       <c r="C87" s="48">
-        <v>85</v>
-      </c>
-      <c r="D87" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="D87" s="81"/>
       <c r="E87" s="82"/>
       <c r="F87" s="19"/>
       <c r="G87" s="20"/>
@@ -9154,9 +9356,9 @@
       <c r="A88" s="41"/>
       <c r="B88" s="14"/>
       <c r="C88" s="48">
-        <v>86</v>
-      </c>
-      <c r="D88" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="D88" s="81"/>
       <c r="E88" s="82"/>
       <c r="F88" s="19"/>
       <c r="G88" s="20"/>
@@ -9170,7 +9372,7 @@
       <c r="A89" s="41"/>
       <c r="B89" s="14"/>
       <c r="C89" s="48">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="82"/>
@@ -9186,7 +9388,7 @@
       <c r="A90" s="41"/>
       <c r="B90" s="14"/>
       <c r="C90" s="48">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="82"/>
@@ -9202,7 +9404,7 @@
       <c r="A91" s="41"/>
       <c r="B91" s="14"/>
       <c r="C91" s="48">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="82"/>
@@ -9218,7 +9420,7 @@
       <c r="A92" s="41"/>
       <c r="B92" s="14"/>
       <c r="C92" s="48">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="82"/>
@@ -9234,9 +9436,9 @@
       <c r="A93" s="41"/>
       <c r="B93" s="14"/>
       <c r="C93" s="48">
-        <v>91</v>
-      </c>
-      <c r="D93" s="81"/>
+        <v>89</v>
+      </c>
+      <c r="D93" s="3"/>
       <c r="E93" s="82"/>
       <c r="F93" s="19"/>
       <c r="G93" s="20"/>
@@ -9250,7 +9452,7 @@
       <c r="A94" s="41"/>
       <c r="B94" s="14"/>
       <c r="C94" s="48">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="82"/>
@@ -9266,9 +9468,9 @@
       <c r="A95" s="41"/>
       <c r="B95" s="14"/>
       <c r="C95" s="48">
-        <v>93</v>
-      </c>
-      <c r="D95" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="D95" s="81"/>
       <c r="E95" s="82"/>
       <c r="F95" s="19"/>
       <c r="G95" s="20"/>
@@ -9282,11 +9484,11 @@
       <c r="A96" s="41"/>
       <c r="B96" s="14"/>
       <c r="C96" s="48">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="82"/>
-      <c r="F96" s="16"/>
+      <c r="F96" s="19"/>
       <c r="G96" s="20"/>
       <c r="H96" s="20"/>
       <c r="I96" s="20"/>
@@ -9298,11 +9500,11 @@
       <c r="A97" s="41"/>
       <c r="B97" s="14"/>
       <c r="C97" s="48">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="82"/>
-      <c r="F97" s="16"/>
+      <c r="F97" s="19"/>
       <c r="G97" s="20"/>
       <c r="H97" s="20"/>
       <c r="I97" s="20"/>
@@ -9314,11 +9516,11 @@
       <c r="A98" s="41"/>
       <c r="B98" s="14"/>
       <c r="C98" s="48">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="82"/>
-      <c r="F98" s="19"/>
+      <c r="F98" s="16"/>
       <c r="G98" s="20"/>
       <c r="H98" s="20"/>
       <c r="I98" s="20"/>
@@ -9330,11 +9532,11 @@
       <c r="A99" s="41"/>
       <c r="B99" s="14"/>
       <c r="C99" s="48">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="82"/>
-      <c r="F99" s="19"/>
+      <c r="F99" s="16"/>
       <c r="G99" s="20"/>
       <c r="H99" s="20"/>
       <c r="I99" s="20"/>
@@ -9346,7 +9548,7 @@
       <c r="A100" s="41"/>
       <c r="B100" s="14"/>
       <c r="C100" s="48">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="82"/>
@@ -9357,16 +9559,14 @@
       <c r="J100" s="4"/>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
-      <c r="IK100"/>
-      <c r="IL100"/>
     </row>
     <row r="101" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="41"/>
       <c r="B101" s="14"/>
       <c r="C101" s="48">
-        <v>99</v>
-      </c>
-      <c r="D101" s="81"/>
+        <v>97</v>
+      </c>
+      <c r="D101" s="3"/>
       <c r="E101" s="82"/>
       <c r="F101" s="19"/>
       <c r="G101" s="20"/>
@@ -9380,7 +9580,7 @@
       <c r="A102" s="41"/>
       <c r="B102" s="14"/>
       <c r="C102" s="48">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="82"/>
@@ -9391,14 +9591,16 @@
       <c r="J102" s="4"/>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
+      <c r="IK102"/>
+      <c r="IL102"/>
     </row>
     <row r="103" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="41"/>
       <c r="B103" s="14"/>
       <c r="C103" s="48">
-        <v>101</v>
-      </c>
-      <c r="D103" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="D103" s="81"/>
       <c r="E103" s="82"/>
       <c r="F103" s="19"/>
       <c r="G103" s="20"/>
@@ -9412,9 +9614,9 @@
       <c r="A104" s="41"/>
       <c r="B104" s="14"/>
       <c r="C104" s="48">
-        <v>102</v>
-      </c>
-      <c r="D104" s="81"/>
+        <v>100</v>
+      </c>
+      <c r="D104" s="3"/>
       <c r="E104" s="82"/>
       <c r="F104" s="19"/>
       <c r="G104" s="20"/>
@@ -9428,7 +9630,7 @@
       <c r="A105" s="41"/>
       <c r="B105" s="14"/>
       <c r="C105" s="48">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="82"/>
@@ -9444,9 +9646,9 @@
       <c r="A106" s="41"/>
       <c r="B106" s="14"/>
       <c r="C106" s="48">
-        <v>104</v>
-      </c>
-      <c r="D106" s="3"/>
+        <v>102</v>
+      </c>
+      <c r="D106" s="81"/>
       <c r="E106" s="82"/>
       <c r="F106" s="19"/>
       <c r="G106" s="20"/>
@@ -9460,7 +9662,7 @@
       <c r="A107" s="41"/>
       <c r="B107" s="14"/>
       <c r="C107" s="48">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="82"/>
@@ -9476,7 +9678,7 @@
       <c r="A108" s="41"/>
       <c r="B108" s="14"/>
       <c r="C108" s="48">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="82"/>
@@ -9492,7 +9694,7 @@
       <c r="A109" s="41"/>
       <c r="B109" s="14"/>
       <c r="C109" s="48">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="82"/>
@@ -9508,9 +9710,9 @@
       <c r="A110" s="41"/>
       <c r="B110" s="14"/>
       <c r="C110" s="48">
-        <v>108</v>
-      </c>
-      <c r="D110" s="81"/>
+        <v>106</v>
+      </c>
+      <c r="D110" s="3"/>
       <c r="E110" s="82"/>
       <c r="F110" s="19"/>
       <c r="G110" s="20"/>
@@ -9524,7 +9726,7 @@
       <c r="A111" s="41"/>
       <c r="B111" s="14"/>
       <c r="C111" s="48">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="82"/>
@@ -9540,9 +9742,9 @@
       <c r="A112" s="41"/>
       <c r="B112" s="14"/>
       <c r="C112" s="48">
-        <v>110</v>
-      </c>
-      <c r="D112" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="D112" s="81"/>
       <c r="E112" s="82"/>
       <c r="F112" s="19"/>
       <c r="G112" s="20"/>
@@ -9556,7 +9758,7 @@
       <c r="A113" s="41"/>
       <c r="B113" s="14"/>
       <c r="C113" s="48">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="82"/>
@@ -9572,11 +9774,11 @@
       <c r="A114" s="41"/>
       <c r="B114" s="14"/>
       <c r="C114" s="48">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="82"/>
-      <c r="F114" s="16"/>
+      <c r="F114" s="19"/>
       <c r="G114" s="20"/>
       <c r="H114" s="20"/>
       <c r="I114" s="20"/>
@@ -9588,10 +9790,10 @@
       <c r="A115" s="41"/>
       <c r="B115" s="14"/>
       <c r="C115" s="48">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D115" s="3"/>
-      <c r="E115" s="21"/>
+      <c r="E115" s="82"/>
       <c r="F115" s="19"/>
       <c r="G115" s="20"/>
       <c r="H115" s="20"/>
@@ -9604,11 +9806,11 @@
       <c r="A116" s="41"/>
       <c r="B116" s="14"/>
       <c r="C116" s="48">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="82"/>
-      <c r="F116" s="19"/>
+      <c r="F116" s="16"/>
       <c r="G116" s="20"/>
       <c r="H116" s="20"/>
       <c r="I116" s="20"/>
@@ -9620,10 +9822,10 @@
       <c r="A117" s="41"/>
       <c r="B117" s="14"/>
       <c r="C117" s="48">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D117" s="3"/>
-      <c r="E117" s="82"/>
+      <c r="E117" s="21"/>
       <c r="F117" s="19"/>
       <c r="G117" s="20"/>
       <c r="H117" s="20"/>
@@ -9636,7 +9838,7 @@
       <c r="A118" s="41"/>
       <c r="B118" s="14"/>
       <c r="C118" s="48">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="82"/>
@@ -9652,7 +9854,7 @@
       <c r="A119" s="41"/>
       <c r="B119" s="14"/>
       <c r="C119" s="48">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="82"/>
@@ -9668,7 +9870,7 @@
       <c r="A120" s="41"/>
       <c r="B120" s="14"/>
       <c r="C120" s="48">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="82"/>
@@ -9684,7 +9886,7 @@
       <c r="A121" s="41"/>
       <c r="B121" s="14"/>
       <c r="C121" s="48">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="82"/>
@@ -9700,10 +9902,10 @@
       <c r="A122" s="41"/>
       <c r="B122" s="14"/>
       <c r="C122" s="48">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D122" s="3"/>
-      <c r="E122" s="2"/>
+      <c r="E122" s="82"/>
       <c r="F122" s="19"/>
       <c r="G122" s="20"/>
       <c r="H122" s="20"/>
@@ -9716,7 +9918,7 @@
       <c r="A123" s="41"/>
       <c r="B123" s="14"/>
       <c r="C123" s="48">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="82"/>
@@ -9732,10 +9934,10 @@
       <c r="A124" s="41"/>
       <c r="B124" s="14"/>
       <c r="C124" s="48">
-        <v>122</v>
-      </c>
-      <c r="D124" s="81"/>
-      <c r="E124" s="82"/>
+        <v>120</v>
+      </c>
+      <c r="D124" s="3"/>
+      <c r="E124" s="2"/>
       <c r="F124" s="19"/>
       <c r="G124" s="20"/>
       <c r="H124" s="20"/>
@@ -9748,7 +9950,7 @@
       <c r="A125" s="41"/>
       <c r="B125" s="14"/>
       <c r="C125" s="48">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="82"/>
@@ -9764,9 +9966,9 @@
       <c r="A126" s="41"/>
       <c r="B126" s="14"/>
       <c r="C126" s="48">
-        <v>124</v>
-      </c>
-      <c r="D126" s="3"/>
+        <v>122</v>
+      </c>
+      <c r="D126" s="81"/>
       <c r="E126" s="82"/>
       <c r="F126" s="19"/>
       <c r="G126" s="20"/>
@@ -9780,7 +9982,7 @@
       <c r="A127" s="41"/>
       <c r="B127" s="14"/>
       <c r="C127" s="48">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="82"/>
@@ -9796,7 +9998,7 @@
       <c r="A128" s="41"/>
       <c r="B128" s="14"/>
       <c r="C128" s="48">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="82"/>
@@ -9812,9 +10014,9 @@
       <c r="A129" s="41"/>
       <c r="B129" s="14"/>
       <c r="C129" s="48">
-        <v>127</v>
-      </c>
-      <c r="D129" s="81"/>
+        <v>125</v>
+      </c>
+      <c r="D129" s="3"/>
       <c r="E129" s="82"/>
       <c r="F129" s="19"/>
       <c r="G129" s="20"/>
@@ -9828,10 +10030,10 @@
       <c r="A130" s="41"/>
       <c r="B130" s="14"/>
       <c r="C130" s="48">
-        <v>128</v>
-      </c>
-      <c r="D130" s="37"/>
-      <c r="E130" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="D130" s="3"/>
+      <c r="E130" s="82"/>
       <c r="F130" s="19"/>
       <c r="G130" s="20"/>
       <c r="H130" s="20"/>
@@ -9844,9 +10046,9 @@
       <c r="A131" s="41"/>
       <c r="B131" s="14"/>
       <c r="C131" s="48">
-        <v>129</v>
-      </c>
-      <c r="D131" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="D131" s="81"/>
       <c r="E131" s="82"/>
       <c r="F131" s="19"/>
       <c r="G131" s="20"/>
@@ -9860,10 +10062,10 @@
       <c r="A132" s="41"/>
       <c r="B132" s="14"/>
       <c r="C132" s="48">
-        <v>130</v>
-      </c>
-      <c r="D132" s="3"/>
-      <c r="E132" s="21"/>
+        <v>128</v>
+      </c>
+      <c r="D132" s="37"/>
+      <c r="E132" s="2"/>
       <c r="F132" s="19"/>
       <c r="G132" s="20"/>
       <c r="H132" s="20"/>
@@ -9876,7 +10078,7 @@
       <c r="A133" s="41"/>
       <c r="B133" s="14"/>
       <c r="C133" s="48">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="82"/>
@@ -9892,7 +10094,7 @@
       <c r="A134" s="41"/>
       <c r="B134" s="14"/>
       <c r="C134" s="48">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="21"/>
@@ -9908,10 +10110,10 @@
       <c r="A135" s="41"/>
       <c r="B135" s="14"/>
       <c r="C135" s="48">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D135" s="3"/>
-      <c r="E135" s="21"/>
+      <c r="E135" s="82"/>
       <c r="F135" s="19"/>
       <c r="G135" s="20"/>
       <c r="H135" s="20"/>
@@ -9924,10 +10126,10 @@
       <c r="A136" s="41"/>
       <c r="B136" s="14"/>
       <c r="C136" s="48">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D136" s="3"/>
-      <c r="E136" s="82"/>
+      <c r="E136" s="21"/>
       <c r="F136" s="19"/>
       <c r="G136" s="20"/>
       <c r="H136" s="20"/>
@@ -9940,7 +10142,7 @@
       <c r="A137" s="41"/>
       <c r="B137" s="14"/>
       <c r="C137" s="48">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="21"/>
@@ -9956,9 +10158,9 @@
       <c r="A138" s="41"/>
       <c r="B138" s="14"/>
       <c r="C138" s="48">
-        <v>136</v>
-      </c>
-      <c r="D138" s="81"/>
+        <v>134</v>
+      </c>
+      <c r="D138" s="3"/>
       <c r="E138" s="82"/>
       <c r="F138" s="19"/>
       <c r="G138" s="20"/>
@@ -9972,10 +10174,10 @@
       <c r="A139" s="41"/>
       <c r="B139" s="14"/>
       <c r="C139" s="48">
-        <v>137</v>
-      </c>
-      <c r="D139" s="81"/>
-      <c r="E139" s="82"/>
+        <v>135</v>
+      </c>
+      <c r="D139" s="3"/>
+      <c r="E139" s="21"/>
       <c r="F139" s="19"/>
       <c r="G139" s="20"/>
       <c r="H139" s="20"/>
@@ -9988,7 +10190,7 @@
       <c r="A140" s="41"/>
       <c r="B140" s="14"/>
       <c r="C140" s="48">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D140" s="81"/>
       <c r="E140" s="82"/>
@@ -10004,9 +10206,9 @@
       <c r="A141" s="41"/>
       <c r="B141" s="14"/>
       <c r="C141" s="48">
-        <v>139</v>
-      </c>
-      <c r="D141" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="D141" s="81"/>
       <c r="E141" s="82"/>
       <c r="F141" s="19"/>
       <c r="G141" s="20"/>
@@ -10020,9 +10222,9 @@
       <c r="A142" s="41"/>
       <c r="B142" s="14"/>
       <c r="C142" s="48">
-        <v>140</v>
-      </c>
-      <c r="D142" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="D142" s="81"/>
       <c r="E142" s="82"/>
       <c r="F142" s="19"/>
       <c r="G142" s="20"/>
@@ -10036,10 +10238,10 @@
       <c r="A143" s="41"/>
       <c r="B143" s="14"/>
       <c r="C143" s="48">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D143" s="3"/>
-      <c r="E143" s="2"/>
+      <c r="E143" s="82"/>
       <c r="F143" s="19"/>
       <c r="G143" s="20"/>
       <c r="H143" s="20"/>
@@ -10052,7 +10254,7 @@
       <c r="A144" s="41"/>
       <c r="B144" s="14"/>
       <c r="C144" s="48">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="82"/>
@@ -10068,10 +10270,10 @@
       <c r="A145" s="41"/>
       <c r="B145" s="14"/>
       <c r="C145" s="48">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D145" s="3"/>
-      <c r="E145" s="82"/>
+      <c r="E145" s="2"/>
       <c r="F145" s="19"/>
       <c r="G145" s="20"/>
       <c r="H145" s="20"/>
@@ -10084,10 +10286,10 @@
       <c r="A146" s="41"/>
       <c r="B146" s="14"/>
       <c r="C146" s="48">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D146" s="3"/>
-      <c r="E146" s="21"/>
+      <c r="E146" s="82"/>
       <c r="F146" s="19"/>
       <c r="G146" s="20"/>
       <c r="H146" s="20"/>
@@ -10100,9 +10302,9 @@
       <c r="A147" s="41"/>
       <c r="B147" s="14"/>
       <c r="C147" s="48">
-        <v>144</v>
-      </c>
-      <c r="D147" s="37"/>
+        <v>142</v>
+      </c>
+      <c r="D147" s="3"/>
       <c r="E147" s="82"/>
       <c r="F147" s="19"/>
       <c r="G147" s="20"/>
@@ -10116,10 +10318,10 @@
       <c r="A148" s="41"/>
       <c r="B148" s="14"/>
       <c r="C148" s="48">
-        <v>145</v>
-      </c>
-      <c r="D148" s="81"/>
-      <c r="E148" s="82"/>
+        <v>143</v>
+      </c>
+      <c r="D148" s="3"/>
+      <c r="E148" s="21"/>
       <c r="F148" s="19"/>
       <c r="G148" s="20"/>
       <c r="H148" s="20"/>
@@ -10131,9 +10333,9 @@
       <c r="A149" s="41"/>
       <c r="B149" s="14"/>
       <c r="C149" s="48">
-        <v>146</v>
-      </c>
-      <c r="D149" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="D149" s="37"/>
       <c r="E149" s="82"/>
       <c r="F149" s="19"/>
       <c r="G149" s="20"/>
@@ -10147,10 +10349,10 @@
       <c r="A150" s="41"/>
       <c r="B150" s="14"/>
       <c r="C150" s="48">
-        <v>147</v>
-      </c>
-      <c r="D150" s="3"/>
-      <c r="E150" s="21"/>
+        <v>145</v>
+      </c>
+      <c r="D150" s="81"/>
+      <c r="E150" s="82"/>
       <c r="F150" s="19"/>
       <c r="G150" s="20"/>
       <c r="H150" s="20"/>
@@ -10163,10 +10365,10 @@
       <c r="A151" s="41"/>
       <c r="B151" s="14"/>
       <c r="C151" s="48">
-        <v>148</v>
-      </c>
-      <c r="D151" s="37"/>
-      <c r="E151" s="21"/>
+        <v>146</v>
+      </c>
+      <c r="D151" s="3"/>
+      <c r="E151" s="82"/>
       <c r="F151" s="19"/>
       <c r="G151" s="20"/>
       <c r="H151" s="20"/>
@@ -10179,9 +10381,9 @@
       <c r="A152" s="41"/>
       <c r="B152" s="14"/>
       <c r="C152" s="48">
-        <v>148</v>
-      </c>
-      <c r="D152" s="37"/>
+        <v>147</v>
+      </c>
+      <c r="D152" s="3"/>
       <c r="E152" s="21"/>
       <c r="F152" s="19"/>
       <c r="G152" s="20"/>
@@ -10195,10 +10397,10 @@
       <c r="A153" s="41"/>
       <c r="B153" s="14"/>
       <c r="C153" s="48">
-        <v>149</v>
-      </c>
-      <c r="D153" s="3"/>
-      <c r="E153" s="82"/>
+        <v>148</v>
+      </c>
+      <c r="D153" s="37"/>
+      <c r="E153" s="21"/>
       <c r="F153" s="19"/>
       <c r="G153" s="20"/>
       <c r="H153" s="20"/>
@@ -10211,10 +10413,10 @@
       <c r="A154" s="41"/>
       <c r="B154" s="14"/>
       <c r="C154" s="48">
-        <v>149.69999999999999</v>
-      </c>
-      <c r="D154" s="81"/>
-      <c r="E154" s="82"/>
+        <v>148</v>
+      </c>
+      <c r="D154" s="37"/>
+      <c r="E154" s="21"/>
       <c r="F154" s="19"/>
       <c r="G154" s="20"/>
       <c r="H154" s="20"/>
@@ -10227,9 +10429,9 @@
       <c r="A155" s="41"/>
       <c r="B155" s="14"/>
       <c r="C155" s="48">
-        <v>151</v>
-      </c>
-      <c r="D155" s="81"/>
+        <v>149</v>
+      </c>
+      <c r="D155" s="3"/>
       <c r="E155" s="82"/>
       <c r="F155" s="19"/>
       <c r="G155" s="20"/>
@@ -10243,10 +10445,10 @@
       <c r="A156" s="41"/>
       <c r="B156" s="14"/>
       <c r="C156" s="48">
-        <v>152</v>
-      </c>
-      <c r="D156" s="37"/>
-      <c r="E156" s="21"/>
+        <v>149.69999999999999</v>
+      </c>
+      <c r="D156" s="81"/>
+      <c r="E156" s="82"/>
       <c r="F156" s="19"/>
       <c r="G156" s="20"/>
       <c r="H156" s="20"/>
@@ -10259,10 +10461,10 @@
       <c r="A157" s="41"/>
       <c r="B157" s="14"/>
       <c r="C157" s="48">
-        <v>153</v>
-      </c>
-      <c r="D157" s="37"/>
-      <c r="E157" s="21"/>
+        <v>151</v>
+      </c>
+      <c r="D157" s="81"/>
+      <c r="E157" s="82"/>
       <c r="F157" s="19"/>
       <c r="G157" s="20"/>
       <c r="H157" s="20"/>
@@ -10275,7 +10477,7 @@
       <c r="A158" s="41"/>
       <c r="B158" s="14"/>
       <c r="C158" s="48">
-        <v>154.03</v>
+        <v>152</v>
       </c>
       <c r="D158" s="37"/>
       <c r="E158" s="21"/>
@@ -10291,7 +10493,7 @@
       <c r="A159" s="41"/>
       <c r="B159" s="14"/>
       <c r="C159" s="48">
-        <v>155.06</v>
+        <v>153</v>
       </c>
       <c r="D159" s="37"/>
       <c r="E159" s="21"/>
@@ -10307,7 +10509,7 @@
       <c r="A160" s="41"/>
       <c r="B160" s="14"/>
       <c r="C160" s="48">
-        <v>156.09</v>
+        <v>154.03</v>
       </c>
       <c r="D160" s="37"/>
       <c r="E160" s="21"/>
@@ -10319,11 +10521,11 @@
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
     </row>
-    <row r="161" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="41"/>
       <c r="B161" s="14"/>
       <c r="C161" s="48">
-        <v>157.12</v>
+        <v>155.06</v>
       </c>
       <c r="D161" s="37"/>
       <c r="E161" s="21"/>
@@ -10335,14 +10537,14 @@
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
     </row>
-    <row r="162" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="41"/>
       <c r="B162" s="14"/>
       <c r="C162" s="48">
-        <v>158.15</v>
+        <v>156.09</v>
       </c>
       <c r="D162" s="37"/>
-      <c r="E162" s="18"/>
+      <c r="E162" s="21"/>
       <c r="F162" s="19"/>
       <c r="G162" s="20"/>
       <c r="H162" s="20"/>
@@ -10351,11 +10553,11 @@
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
     </row>
-    <row r="163" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="41"/>
       <c r="B163" s="14"/>
       <c r="C163" s="48">
-        <v>159.18</v>
+        <v>157.12</v>
       </c>
       <c r="D163" s="37"/>
       <c r="E163" s="21"/>
@@ -10367,15 +10569,15 @@
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
-    <row r="164" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="41"/>
       <c r="B164" s="14"/>
       <c r="C164" s="48">
-        <v>160.21</v>
+        <v>158.15</v>
       </c>
       <c r="D164" s="37"/>
-      <c r="E164" s="21"/>
-      <c r="F164" s="20"/>
+      <c r="E164" s="18"/>
+      <c r="F164" s="19"/>
       <c r="G164" s="20"/>
       <c r="H164" s="20"/>
       <c r="I164" s="20"/>
@@ -10383,11 +10585,11 @@
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
     </row>
-    <row r="165" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="41"/>
       <c r="B165" s="14"/>
       <c r="C165" s="48">
-        <v>161.24</v>
+        <v>159.18</v>
       </c>
       <c r="D165" s="37"/>
       <c r="E165" s="21"/>
@@ -10399,15 +10601,15 @@
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
     </row>
-    <row r="166" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="41"/>
       <c r="B166" s="14"/>
       <c r="C166" s="48">
-        <v>162.27000000000001</v>
-      </c>
-      <c r="D166" s="3"/>
-      <c r="E166" s="82"/>
-      <c r="F166" s="19"/>
+        <v>160.21</v>
+      </c>
+      <c r="D166" s="37"/>
+      <c r="E166" s="21"/>
+      <c r="F166" s="20"/>
       <c r="G166" s="20"/>
       <c r="H166" s="20"/>
       <c r="I166" s="20"/>
@@ -10415,11 +10617,11 @@
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
     </row>
-    <row r="167" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="41"/>
       <c r="B167" s="14"/>
       <c r="C167" s="48">
-        <v>163.30000000000001</v>
+        <v>161.24</v>
       </c>
       <c r="D167" s="37"/>
       <c r="E167" s="21"/>
@@ -10431,14 +10633,14 @@
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
     </row>
-    <row r="168" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="41"/>
       <c r="B168" s="14"/>
       <c r="C168" s="48">
-        <v>164.33</v>
-      </c>
-      <c r="D168" s="37"/>
-      <c r="E168" s="18"/>
+        <v>162.27000000000001</v>
+      </c>
+      <c r="D168" s="3"/>
+      <c r="E168" s="82"/>
       <c r="F168" s="19"/>
       <c r="G168" s="20"/>
       <c r="H168" s="20"/>
@@ -10447,11 +10649,11 @@
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
-    <row r="169" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="41"/>
       <c r="B169" s="14"/>
       <c r="C169" s="48">
-        <v>165.36</v>
+        <v>163.30000000000001</v>
       </c>
       <c r="D169" s="37"/>
       <c r="E169" s="21"/>
@@ -10463,13 +10665,13 @@
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
     </row>
-    <row r="170" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="41"/>
       <c r="B170" s="14"/>
       <c r="C170" s="48">
-        <v>166.39</v>
-      </c>
-      <c r="D170" s="15"/>
+        <v>164.33</v>
+      </c>
+      <c r="D170" s="37"/>
       <c r="E170" s="18"/>
       <c r="F170" s="19"/>
       <c r="G170" s="20"/>
@@ -10479,14 +10681,14 @@
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
     </row>
-    <row r="171" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="41"/>
       <c r="B171" s="14"/>
       <c r="C171" s="48">
-        <v>167.42</v>
-      </c>
-      <c r="D171" s="15"/>
-      <c r="E171" s="18"/>
+        <v>165.36</v>
+      </c>
+      <c r="D171" s="37"/>
+      <c r="E171" s="21"/>
       <c r="F171" s="19"/>
       <c r="G171" s="20"/>
       <c r="H171" s="20"/>
@@ -10495,11 +10697,11 @@
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
     </row>
-    <row r="172" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="41"/>
       <c r="B172" s="14"/>
       <c r="C172" s="48">
-        <v>168.45</v>
+        <v>166.39</v>
       </c>
       <c r="D172" s="15"/>
       <c r="E172" s="18"/>
@@ -10507,15 +10709,15 @@
       <c r="G172" s="20"/>
       <c r="H172" s="20"/>
       <c r="I172" s="20"/>
-      <c r="J172" s="44"/>
+      <c r="J172" s="4"/>
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
     </row>
-    <row r="173" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="41"/>
       <c r="B173" s="14"/>
       <c r="C173" s="48">
-        <v>169.48</v>
+        <v>167.42</v>
       </c>
       <c r="D173" s="15"/>
       <c r="E173" s="18"/>
@@ -10523,15 +10725,15 @@
       <c r="G173" s="20"/>
       <c r="H173" s="20"/>
       <c r="I173" s="20"/>
-      <c r="J173" s="44"/>
+      <c r="J173" s="4"/>
       <c r="K173" s="2"/>
       <c r="L173" s="2"/>
     </row>
-    <row r="174" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="41"/>
       <c r="B174" s="14"/>
       <c r="C174" s="48">
-        <v>170.51</v>
+        <v>168.45</v>
       </c>
       <c r="D174" s="15"/>
       <c r="E174" s="18"/>
@@ -10543,11 +10745,13 @@
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
     </row>
-    <row r="175" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="41"/>
       <c r="B175" s="14"/>
-      <c r="C175" s="48"/>
-      <c r="D175" s="37"/>
+      <c r="C175" s="48">
+        <v>169.48</v>
+      </c>
+      <c r="D175" s="15"/>
       <c r="E175" s="18"/>
       <c r="F175" s="19"/>
       <c r="G175" s="20"/>
@@ -10556,65 +10760,67 @@
       <c r="J175" s="44"/>
       <c r="K175" s="2"/>
       <c r="L175" s="2"/>
-      <c r="IL175"/>
-    </row>
-    <row r="176" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="42"/>
-      <c r="B176" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C176" s="49"/>
-      <c r="D176" s="29"/>
-      <c r="E176" s="30"/>
-      <c r="F176" s="31">
-        <f>SUM(F3:F175)</f>
-        <v>0</v>
-      </c>
-      <c r="G176" s="32">
-        <f>SUM(G3:G175)</f>
-        <v>-1792.15</v>
-      </c>
-      <c r="H176" s="32">
-        <f>SUM(H3:H175)</f>
-        <v>0</v>
-      </c>
-      <c r="I176" s="32">
-        <f>SUM(I3:I175)</f>
-        <v>-3163.41</v>
-      </c>
-      <c r="J176" s="2"/>
+    </row>
+    <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="41"/>
+      <c r="B176" s="14"/>
+      <c r="C176" s="48">
+        <v>170.51</v>
+      </c>
+      <c r="D176" s="15"/>
+      <c r="E176" s="18"/>
+      <c r="F176" s="19"/>
+      <c r="G176" s="20"/>
+      <c r="H176" s="20"/>
+      <c r="I176" s="20"/>
+      <c r="J176" s="44"/>
       <c r="K176" s="2"/>
       <c r="L176" s="2"/>
     </row>
-    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="42"/>
-      <c r="B177" s="17"/>
-      <c r="C177" s="17"/>
-      <c r="D177" s="17"/>
-      <c r="E177" s="17"/>
-      <c r="F177" s="17"/>
-      <c r="G177" s="17"/>
-      <c r="H177" s="17"/>
-      <c r="I177" s="17"/>
-      <c r="J177" s="2"/>
+    <row r="177" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="41"/>
+      <c r="B177" s="14"/>
+      <c r="C177" s="48"/>
+      <c r="D177" s="37"/>
+      <c r="E177" s="18"/>
+      <c r="F177" s="19"/>
+      <c r="G177" s="20"/>
+      <c r="H177" s="20"/>
+      <c r="I177" s="20"/>
+      <c r="J177" s="44"/>
       <c r="K177" s="2"/>
       <c r="L177" s="2"/>
-    </row>
-    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="IL177"/>
+    </row>
+    <row r="178" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="42"/>
-      <c r="B178" s="17"/>
-      <c r="C178" s="17"/>
-      <c r="D178" s="17"/>
-      <c r="E178" s="17"/>
-      <c r="F178" s="17"/>
-      <c r="G178" s="17"/>
-      <c r="H178" s="17"/>
-      <c r="I178" s="17"/>
+      <c r="B178" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="49"/>
+      <c r="D178" s="29"/>
+      <c r="E178" s="30"/>
+      <c r="F178" s="31">
+        <f>SUM(F3:F177)</f>
+        <v>0</v>
+      </c>
+      <c r="G178" s="32">
+        <f>SUM(G3:G177)</f>
+        <v>-2328.66</v>
+      </c>
+      <c r="H178" s="32">
+        <f>SUM(H3:H177)</f>
+        <v>0</v>
+      </c>
+      <c r="I178" s="32">
+        <f>SUM(I3:I177)</f>
+        <v>-3185.91</v>
+      </c>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
     </row>
-    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="42"/>
       <c r="B179" s="17"/>
       <c r="C179" s="17"/>
@@ -10628,7 +10834,7 @@
       <c r="K179" s="2"/>
       <c r="L179" s="2"/>
     </row>
-    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="42"/>
       <c r="B180" s="17"/>
       <c r="C180" s="17"/>
@@ -10642,7 +10848,7 @@
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
     </row>
-    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="42"/>
       <c r="B181" s="17"/>
       <c r="C181" s="17"/>
@@ -10656,7 +10862,7 @@
       <c r="K181" s="2"/>
       <c r="L181" s="2"/>
     </row>
-    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="42"/>
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
@@ -10670,7 +10876,7 @@
       <c r="K182" s="2"/>
       <c r="L182" s="2"/>
     </row>
-    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="42"/>
       <c r="B183" s="17"/>
       <c r="C183" s="17"/>
@@ -10684,7 +10890,7 @@
       <c r="K183" s="2"/>
       <c r="L183" s="2"/>
     </row>
-    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="42"/>
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
@@ -10698,7 +10904,7 @@
       <c r="K184" s="2"/>
       <c r="L184" s="2"/>
     </row>
-    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="42"/>
       <c r="B185" s="17"/>
       <c r="C185" s="17"/>
@@ -10712,7 +10918,7 @@
       <c r="K185" s="2"/>
       <c r="L185" s="2"/>
     </row>
-    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="42"/>
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
@@ -10726,7 +10932,7 @@
       <c r="K186" s="2"/>
       <c r="L186" s="2"/>
     </row>
-    <row r="187" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="42"/>
       <c r="B187" s="17"/>
       <c r="C187" s="17"/>
@@ -10740,7 +10946,7 @@
       <c r="K187" s="2"/>
       <c r="L187" s="2"/>
     </row>
-    <row r="188" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="42"/>
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
@@ -10754,7 +10960,7 @@
       <c r="K188" s="2"/>
       <c r="L188" s="2"/>
     </row>
-    <row r="189" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="42"/>
       <c r="B189" s="17"/>
       <c r="C189" s="17"/>
@@ -10768,7 +10974,7 @@
       <c r="K189" s="2"/>
       <c r="L189" s="2"/>
     </row>
-    <row r="190" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="42"/>
       <c r="B190" s="17"/>
       <c r="C190" s="17"/>
@@ -10782,7 +10988,7 @@
       <c r="K190" s="2"/>
       <c r="L190" s="2"/>
     </row>
-    <row r="191" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="42"/>
       <c r="B191" s="17"/>
       <c r="C191" s="17"/>
@@ -10796,7 +11002,7 @@
       <c r="K191" s="2"/>
       <c r="L191" s="2"/>
     </row>
-    <row r="192" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:246" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="42"/>
       <c r="B192" s="17"/>
       <c r="C192" s="17"/>
@@ -11479,123 +11685,159 @@
       <c r="H240" s="17"/>
       <c r="I240" s="17"/>
       <c r="J240" s="2"/>
+      <c r="K240" s="2"/>
       <c r="L240" s="2"/>
     </row>
-    <row r="241" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="42"/>
       <c r="B241" s="17"/>
       <c r="C241" s="17"/>
+      <c r="D241" s="17"/>
+      <c r="E241" s="17"/>
+      <c r="F241" s="17"/>
+      <c r="G241" s="17"/>
+      <c r="H241" s="17"/>
       <c r="I241" s="17"/>
-    </row>
-    <row r="242" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J241" s="2"/>
+      <c r="K241" s="2"/>
+    </row>
+    <row r="242" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="42"/>
       <c r="B242" s="17"/>
+      <c r="C242" s="17"/>
+      <c r="D242" s="17"/>
+      <c r="E242" s="17"/>
+      <c r="F242" s="17"/>
+      <c r="G242" s="17"/>
+      <c r="H242" s="17"/>
       <c r="I242" s="17"/>
+      <c r="J242" s="2"/>
+    </row>
+    <row r="243" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B243" s="17"/>
+      <c r="C243" s="17"/>
+      <c r="I243" s="17"/>
+    </row>
+    <row r="244" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B244" s="17"/>
+      <c r="I244" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:J171" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="B2:J173" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A240 E131:E142">
-    <cfRule type="cellIs" dxfId="18" priority="481" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A3:A242 E33 E41:E123 E133:E144">
+    <cfRule type="cellIs" dxfId="20" priority="484" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B127:B140">
-    <cfRule type="cellIs" dxfId="17" priority="464" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="B129:B142">
+    <cfRule type="cellIs" dxfId="19" priority="467" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B154:B242">
-    <cfRule type="cellIs" dxfId="16" priority="21" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="B156:B244">
+    <cfRule type="cellIs" dxfId="18" priority="24" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C153 C155 C157 C159 C161 C163 C165 C171 C173">
-    <cfRule type="cellIs" dxfId="15" priority="22" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C155 C157 C159 C161 C163 C165 C167 C173 C175">
+    <cfRule type="cellIs" dxfId="17" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C175:C241 J177 I177:I242">
-    <cfRule type="cellIs" dxfId="14" priority="711" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C177:C243 J179 I179:I244">
+    <cfRule type="cellIs" dxfId="16" priority="714" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D130">
-    <cfRule type="cellIs" dxfId="13" priority="479" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D132">
+    <cfRule type="cellIs" dxfId="15" priority="482" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D147">
-    <cfRule type="cellIs" dxfId="12" priority="66" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D149">
+    <cfRule type="cellIs" dxfId="14" priority="69" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D151:D152">
-    <cfRule type="cellIs" dxfId="11" priority="450" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D153:D154">
+    <cfRule type="cellIs" dxfId="13" priority="453" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D156:D161">
-    <cfRule type="cellIs" dxfId="10" priority="7" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D158:D163">
+    <cfRule type="cellIs" dxfId="12" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D162:E163 D164:D165 C167:D167 D168:E168 C169:D169">
-    <cfRule type="cellIs" dxfId="9" priority="14" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D164:E165 D166:D167 C169:D169 D170:E170 C171:D171">
+    <cfRule type="cellIs" dxfId="11" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D175:E177">
-    <cfRule type="cellIs" dxfId="8" priority="16" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D177:E179">
+    <cfRule type="cellIs" dxfId="10" priority="19" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D177:H240">
-    <cfRule type="cellIs" dxfId="7" priority="663" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D179:H242">
+    <cfRule type="cellIs" dxfId="9" priority="666" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E123:E129 E144:E161 E15 E21 E24:E121">
-    <cfRule type="cellIs" dxfId="6" priority="2" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E125:E131 E146:E163">
+    <cfRule type="cellIs" dxfId="8" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E164:E167">
-    <cfRule type="cellIs" dxfId="5" priority="4" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E35:E37">
+    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E169:E174">
-    <cfRule type="cellIs" dxfId="4" priority="3" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E166:E169">
+    <cfRule type="cellIs" dxfId="6" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F62:F63">
-    <cfRule type="cellIs" dxfId="3" priority="372" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E171:E176">
+    <cfRule type="cellIs" dxfId="5" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F66:F67">
-    <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F64:F65">
+    <cfRule type="cellIs" dxfId="4" priority="375" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F97">
-    <cfRule type="cellIs" dxfId="1" priority="124" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F68:F69">
+    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F114">
-    <cfRule type="cellIs" dxfId="0" priority="8" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F98:F99">
+    <cfRule type="cellIs" dxfId="2" priority="127" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F116">
+    <cfRule type="cellIs" dxfId="1" priority="11" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:E20">
+    <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E53:E121 E131:E142 E123:E129 E144:E175 E3:E4 E7:E8 E11 E13 E15 E21 E24:E51" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E54" xr:uid="{2159CF4B-2649-4586-B851-DB145DFC2247}">
+      <formula1>$J$1:$J$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E55:E123 E41:E53 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E146:E177 E125:E131 E133:E144 E19:E20" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$L$1:$L$19</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E52" xr:uid="{2159CF4B-2649-4586-B851-DB145DFC2247}">
-      <formula1>$J$1:$J$19</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C89F306-245C-4853-9B0D-6ACB1400E9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BAC7CC-296D-4AD9-8E58-A65DAF98D7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,9 +19,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Ausgaben!$B$2:$J$173</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Einnahmen!$A$2:$H$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Einnahmen!$A$2:$H$107</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Ausgaben!$A$1:$I$177</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Einnahmen!$A$1:$H$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Einnahmen!$A$1:$H$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="101">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -260,6 +260,84 @@
   <si>
     <t>16b</t>
   </si>
+  <si>
+    <t>SPD Miete 11.3.</t>
+  </si>
+  <si>
+    <t>AWO Spendenkasse JHV</t>
+  </si>
+  <si>
+    <t>Bargeld Frühlingserwachen</t>
+  </si>
+  <si>
+    <t>Sumup Frühlingserwachen</t>
+  </si>
+  <si>
+    <t>Abschluss KSK</t>
+  </si>
+  <si>
+    <t>Sumup, AWO Open</t>
+  </si>
+  <si>
+    <t>SPD Getränke</t>
+  </si>
+  <si>
+    <t>Blumen JHV Früchtelädle</t>
+  </si>
+  <si>
+    <t>Jasmin Schulung</t>
+  </si>
+  <si>
+    <t>Ausg Roland Fruehlingserw</t>
+  </si>
+  <si>
+    <t>14a</t>
+  </si>
+  <si>
+    <t>Vereinsförderung Wabu</t>
+  </si>
+  <si>
+    <t>Vereinsförderung Wabu Seniorenarbeit</t>
+  </si>
+  <si>
+    <t>JHV Miete Hdb</t>
+  </si>
+  <si>
+    <t>Sumup Test (Gebühr0,01€)</t>
+  </si>
+  <si>
+    <t>AwOpen Flyer</t>
+  </si>
+  <si>
+    <t>Frühlingserw. Grillgut</t>
+  </si>
+  <si>
+    <t>Frühlingserw. Sonstiges Selgros</t>
+  </si>
+  <si>
+    <t>Frühlingserw. Ausg Rani Indisch</t>
+  </si>
+  <si>
+    <t>Frühlingserw. Ausg Tina Indisch</t>
+  </si>
+  <si>
+    <t>Frühlingserw. Ausg Stefan Getränke</t>
+  </si>
+  <si>
+    <t>Bürgerbus</t>
+  </si>
+  <si>
+    <t>Frühlingserw. Bäcker</t>
+  </si>
+  <si>
+    <t>AwOpen Ausgaben Jasmin</t>
+  </si>
+  <si>
+    <t>Awo Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Awo Einlage Kreis </t>
+  </si>
 </sst>
 </file>
 
@@ -270,7 +348,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; &quot;[$€-2];&quot;-&quot;#,##0.00&quot; &quot;[$€-2]"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -291,6 +369,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -800,7 +885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -914,6 +999,7 @@
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -926,7 +1012,32 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="49">
+  <dxfs count="54">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -1369,7 +1480,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Bernd Wild" refreshedDate="45318.474550925923" createdVersion="4" refreshedVersion="8" minRefreshableVersion="3" recordCount="108" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="D2:H109" sheet="Einnahmen"/>
+    <worksheetSource ref="D2:H110" sheet="Einnahmen"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="Zweck II" numFmtId="0">
@@ -3712,17 +3823,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="45">
+    <format dxfId="50">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3826,17 +3937,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="48">
+    <format dxfId="53">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4977,16 +5088,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3" t="s">
         <v>0</v>
@@ -5359,17 +5470,47 @@
       </c>
     </row>
     <row r="17" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14">
+        <v>46097</v>
+      </c>
       <c r="B17" s="48">
         <v>14</v>
       </c>
+      <c r="C17" s="81" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="20">
+        <v>10</v>
+      </c>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="48">
-        <v>15</v>
+      <c r="A18" s="14">
+        <v>46097</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17">
+        <v>20</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2" t="s">
@@ -5377,139 +5518,237 @@
       </c>
     </row>
     <row r="19" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14">
+        <v>46104</v>
+      </c>
       <c r="B19" s="48">
-        <v>16</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C19" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E19" s="19"/>
+      <c r="F19" s="20">
+        <v>114</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14">
+        <v>46104</v>
+      </c>
       <c r="B20" s="48">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17">
+        <v>52</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
+      <c r="A21" s="14">
+        <v>46108</v>
+      </c>
       <c r="B21" s="48">
-        <v>18</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="18"/>
+        <v>17</v>
+      </c>
+      <c r="C21" s="81" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>12</v>
+      </c>
       <c r="E21" s="19"/>
-      <c r="F21" s="20"/>
+      <c r="F21" s="20">
+        <v>180</v>
+      </c>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
+      <c r="A22" s="14">
+        <v>46108</v>
+      </c>
       <c r="B22" s="48">
-        <v>19</v>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="18"/>
+        <v>18</v>
+      </c>
+      <c r="C22" s="81" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>12</v>
+      </c>
       <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
+      <c r="F22" s="20">
+        <v>360</v>
+      </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
+      <c r="A23" s="14">
+        <v>46108</v>
+      </c>
       <c r="B23" s="48">
-        <v>20</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="16"/>
+        <v>19</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="19"/>
       <c r="F23" s="20"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20">
+        <v>0.99</v>
+      </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
+      <c r="A24" s="14">
+        <v>46111</v>
+      </c>
       <c r="B24" s="48">
-        <v>21</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="17"/>
+        <v>20</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
+      <c r="H24" s="17">
+        <v>937</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
+      <c r="A25" s="14">
+        <v>46111</v>
+      </c>
       <c r="B25" s="48">
-        <v>22</v>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
+        <v>21</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" s="19"/>
+      <c r="F25" s="17"/>
       <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
+      <c r="H25" s="17">
+        <v>302.72000000000003</v>
+      </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
+      <c r="A26" s="14">
+        <v>46113</v>
+      </c>
       <c r="B26" s="48">
-        <v>23</v>
-      </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="19"/>
+        <v>22</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="20"/>
       <c r="F26" s="20"/>
       <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
+      <c r="H26" s="17">
+        <v>4.93</v>
+      </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="18"/>
+      <c r="A27" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B27" s="48">
+        <v>23</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E27" s="19"/>
-      <c r="F27" s="20"/>
+      <c r="F27" s="20">
+        <v>69.5</v>
+      </c>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
+      <c r="A28" s="14">
+        <v>46119</v>
+      </c>
       <c r="B28" s="15">
-        <v>25</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="18"/>
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E28" s="19"/>
-      <c r="F28" s="20"/>
+      <c r="F28" s="20">
+        <v>22.4</v>
+      </c>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
+      <c r="A29" s="14">
+        <v>46120</v>
+      </c>
       <c r="B29" s="15">
-        <v>26</v>
-      </c>
-      <c r="C29" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="D29" s="18"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
@@ -5521,7 +5760,7 @@
     <row r="30" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14"/>
       <c r="B30" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="18"/>
@@ -5535,7 +5774,7 @@
     <row r="31" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14"/>
       <c r="B31" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="18"/>
@@ -5549,9 +5788,9 @@
     <row r="32" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
       <c r="B32" s="15">
-        <v>29</v>
-      </c>
-      <c r="C32" s="15"/>
+        <v>28</v>
+      </c>
+      <c r="C32" s="3"/>
       <c r="D32" s="18"/>
       <c r="E32" s="19"/>
       <c r="F32" s="20"/>
@@ -5563,12 +5802,12 @@
     <row r="33" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
       <c r="B33" s="15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="18"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="17"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="20"/>
       <c r="G33" s="17"/>
       <c r="H33" s="17"/>
       <c r="I33" s="2"/>
@@ -5577,7 +5816,7 @@
     <row r="34" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14"/>
       <c r="B34" s="15">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" s="15"/>
       <c r="D34" s="18"/>
@@ -5591,7 +5830,7 @@
     <row r="35" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14"/>
       <c r="B35" s="15">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="18"/>
@@ -5605,7 +5844,7 @@
     <row r="36" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14"/>
       <c r="B36" s="15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="15"/>
       <c r="D36" s="18"/>
@@ -5619,7 +5858,7 @@
     <row r="37" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="14"/>
       <c r="B37" s="15">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="18"/>
@@ -5632,8 +5871,8 @@
     </row>
     <row r="38" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="14"/>
-      <c r="B38" s="48">
-        <v>35</v>
+      <c r="B38" s="15">
+        <v>34</v>
       </c>
       <c r="C38" s="15"/>
       <c r="D38" s="18"/>
@@ -5646,10 +5885,10 @@
     </row>
     <row r="39" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14"/>
-      <c r="B39" s="15">
-        <v>36</v>
-      </c>
-      <c r="C39" s="37"/>
+      <c r="B39" s="48">
+        <v>35</v>
+      </c>
+      <c r="C39" s="15"/>
       <c r="D39" s="18"/>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
@@ -5661,7 +5900,7 @@
     <row r="40" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14"/>
       <c r="B40" s="15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="37"/>
       <c r="D40" s="18"/>
@@ -5675,9 +5914,9 @@
     <row r="41" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="14"/>
       <c r="B41" s="15">
-        <v>38</v>
-      </c>
-      <c r="C41" s="15"/>
+        <v>37</v>
+      </c>
+      <c r="C41" s="37"/>
       <c r="D41" s="18"/>
       <c r="E41" s="16"/>
       <c r="F41" s="17"/>
@@ -5688,13 +5927,13 @@
     </row>
     <row r="42" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14"/>
-      <c r="B42" s="48">
-        <v>39</v>
-      </c>
-      <c r="C42" s="37"/>
+      <c r="B42" s="15">
+        <v>38</v>
+      </c>
+      <c r="C42" s="15"/>
       <c r="D42" s="18"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="20"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="17"/>
       <c r="G42" s="17"/>
       <c r="H42" s="17"/>
       <c r="I42" s="2"/>
@@ -5702,10 +5941,10 @@
     </row>
     <row r="43" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="14"/>
-      <c r="B43" s="15">
-        <v>40</v>
-      </c>
-      <c r="C43" s="3"/>
+      <c r="B43" s="48">
+        <v>39</v>
+      </c>
+      <c r="C43" s="37"/>
       <c r="D43" s="18"/>
       <c r="E43" s="19"/>
       <c r="F43" s="20"/>
@@ -5717,7 +5956,7 @@
     <row r="44" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14"/>
       <c r="B44" s="15">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="18"/>
@@ -5731,12 +5970,12 @@
     <row r="45" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14"/>
       <c r="B45" s="15">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="18"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="17"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="20"/>
       <c r="G45" s="17"/>
       <c r="H45" s="17"/>
       <c r="I45" s="2"/>
@@ -5745,12 +5984,12 @@
     <row r="46" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14"/>
       <c r="B46" s="15">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="18"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="20"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="17"/>
       <c r="G46" s="17"/>
       <c r="H46" s="17"/>
       <c r="I46" s="2"/>
@@ -5759,12 +5998,12 @@
     <row r="47" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14"/>
       <c r="B47" s="15">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="18"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="17"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="20"/>
       <c r="G47" s="17"/>
       <c r="H47" s="17"/>
       <c r="I47" s="2"/>
@@ -5773,7 +6012,7 @@
     <row r="48" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="14"/>
       <c r="B48" s="15">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="18"/>
@@ -5787,12 +6026,12 @@
     <row r="49" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14"/>
       <c r="B49" s="15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="18"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="20"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="17"/>
       <c r="G49" s="17"/>
       <c r="H49" s="17"/>
       <c r="I49" s="2"/>
@@ -5801,12 +6040,12 @@
     <row r="50" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="14"/>
       <c r="B50" s="15">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="18"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="17"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="20"/>
       <c r="G50" s="17"/>
       <c r="H50" s="17"/>
       <c r="I50" s="2"/>
@@ -5815,11 +6054,11 @@
     <row r="51" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14"/>
       <c r="B51" s="15">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="18"/>
-      <c r="E51" s="19"/>
+      <c r="E51" s="16"/>
       <c r="F51" s="17"/>
       <c r="G51" s="17"/>
       <c r="H51" s="17"/>
@@ -5829,12 +6068,12 @@
     <row r="52" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="14"/>
       <c r="B52" s="15">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="18"/>
       <c r="E52" s="19"/>
-      <c r="F52" s="20"/>
+      <c r="F52" s="17"/>
       <c r="G52" s="17"/>
       <c r="H52" s="17"/>
       <c r="I52" s="2"/>
@@ -5843,12 +6082,12 @@
     <row r="53" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="14"/>
       <c r="B53" s="15">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="18"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="17"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="20"/>
       <c r="G53" s="17"/>
       <c r="H53" s="17"/>
       <c r="I53" s="2"/>
@@ -5857,7 +6096,7 @@
     <row r="54" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14"/>
       <c r="B54" s="15">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="18"/>
@@ -5871,7 +6110,7 @@
     <row r="55" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14"/>
       <c r="B55" s="15">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="18"/>
@@ -5885,7 +6124,7 @@
     <row r="56" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14"/>
       <c r="B56" s="15">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="18"/>
@@ -5899,7 +6138,7 @@
     <row r="57" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="14"/>
       <c r="B57" s="15">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="18"/>
@@ -5913,11 +6152,11 @@
     <row r="58" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="14"/>
       <c r="B58" s="15">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="18"/>
-      <c r="E58" s="19"/>
+      <c r="E58" s="16"/>
       <c r="F58" s="17"/>
       <c r="G58" s="17"/>
       <c r="H58" s="17"/>
@@ -5927,7 +6166,7 @@
     <row r="59" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="14"/>
       <c r="B59" s="15">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="18"/>
@@ -5941,11 +6180,11 @@
     <row r="60" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14"/>
       <c r="B60" s="15">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="18"/>
-      <c r="E60" s="16"/>
+      <c r="E60" s="19"/>
       <c r="F60" s="17"/>
       <c r="G60" s="17"/>
       <c r="H60" s="17"/>
@@ -5954,8 +6193,8 @@
     </row>
     <row r="61" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="14"/>
-      <c r="B61" s="48">
-        <v>58</v>
+      <c r="B61" s="15">
+        <v>57</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="18"/>
@@ -5969,7 +6208,7 @@
     <row r="62" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14"/>
       <c r="B62" s="48">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="18"/>
@@ -5983,9 +6222,9 @@
     <row r="63" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="14"/>
       <c r="B63" s="48">
-        <v>60</v>
-      </c>
-      <c r="C63" s="37"/>
+        <v>59</v>
+      </c>
+      <c r="C63" s="3"/>
       <c r="D63" s="18"/>
       <c r="E63" s="16"/>
       <c r="F63" s="17"/>
@@ -5997,9 +6236,9 @@
     <row r="64" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14"/>
       <c r="B64" s="48">
-        <v>61</v>
-      </c>
-      <c r="C64" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="C64" s="37"/>
       <c r="D64" s="18"/>
       <c r="E64" s="16"/>
       <c r="F64" s="17"/>
@@ -6011,7 +6250,7 @@
     <row r="65" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="14"/>
       <c r="B65" s="48">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="18"/>
@@ -6024,10 +6263,10 @@
     </row>
     <row r="66" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="14"/>
-      <c r="B66" s="15">
-        <v>63</v>
-      </c>
-      <c r="C66" s="15"/>
+      <c r="B66" s="48">
+        <v>62</v>
+      </c>
+      <c r="C66" s="3"/>
       <c r="D66" s="18"/>
       <c r="E66" s="16"/>
       <c r="F66" s="17"/>
@@ -6038,10 +6277,10 @@
     </row>
     <row r="67" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="14"/>
-      <c r="B67" s="48">
-        <v>64</v>
-      </c>
-      <c r="C67" s="37"/>
+      <c r="B67" s="15">
+        <v>63</v>
+      </c>
+      <c r="C67" s="15"/>
       <c r="D67" s="18"/>
       <c r="E67" s="16"/>
       <c r="F67" s="17"/>
@@ -6052,10 +6291,10 @@
     </row>
     <row r="68" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="14"/>
-      <c r="B68" s="15">
-        <v>65</v>
-      </c>
-      <c r="C68" s="15"/>
+      <c r="B68" s="48">
+        <v>64</v>
+      </c>
+      <c r="C68" s="37"/>
       <c r="D68" s="18"/>
       <c r="E68" s="16"/>
       <c r="F68" s="17"/>
@@ -6067,7 +6306,7 @@
     <row r="69" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="14"/>
       <c r="B69" s="15">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="18"/>
@@ -6081,7 +6320,7 @@
     <row r="70" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="14"/>
       <c r="B70" s="15">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C70" s="15"/>
       <c r="D70" s="18"/>
@@ -6095,11 +6334,11 @@
     <row r="71" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="14"/>
       <c r="B71" s="15">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="18"/>
-      <c r="E71" s="19"/>
+      <c r="E71" s="16"/>
       <c r="F71" s="17"/>
       <c r="G71" s="17"/>
       <c r="H71" s="17"/>
@@ -6109,11 +6348,11 @@
     <row r="72" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="14"/>
       <c r="B72" s="15">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C72" s="15"/>
       <c r="D72" s="18"/>
-      <c r="E72" s="16"/>
+      <c r="E72" s="19"/>
       <c r="F72" s="17"/>
       <c r="G72" s="17"/>
       <c r="H72" s="17"/>
@@ -6123,7 +6362,7 @@
     <row r="73" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="14"/>
       <c r="B73" s="15">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="18"/>
@@ -6137,7 +6376,7 @@
     <row r="74" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="14"/>
       <c r="B74" s="15">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C74" s="15"/>
       <c r="D74" s="18"/>
@@ -6151,7 +6390,7 @@
     <row r="75" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="14"/>
       <c r="B75" s="15">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="18"/>
@@ -6165,7 +6404,7 @@
     <row r="76" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="14"/>
       <c r="B76" s="15">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C76" s="15"/>
       <c r="D76" s="18"/>
@@ -6179,7 +6418,7 @@
     <row r="77" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="14"/>
       <c r="B77" s="15">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="18"/>
@@ -6193,7 +6432,7 @@
     <row r="78" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="14"/>
       <c r="B78" s="15">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C78" s="15"/>
       <c r="D78" s="18"/>
@@ -6207,9 +6446,9 @@
     <row r="79" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="14"/>
       <c r="B79" s="15">
-        <v>76</v>
-      </c>
-      <c r="C79" s="37"/>
+        <v>75</v>
+      </c>
+      <c r="C79" s="15"/>
       <c r="D79" s="18"/>
       <c r="E79" s="16"/>
       <c r="F79" s="17"/>
@@ -6221,9 +6460,9 @@
     <row r="80" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="14"/>
       <c r="B80" s="15">
-        <v>77</v>
-      </c>
-      <c r="C80" s="3"/>
+        <v>76</v>
+      </c>
+      <c r="C80" s="37"/>
       <c r="D80" s="18"/>
       <c r="E80" s="16"/>
       <c r="F80" s="17"/>
@@ -6235,7 +6474,7 @@
     <row r="81" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="14"/>
       <c r="B81" s="15">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="18"/>
@@ -6248,13 +6487,13 @@
     </row>
     <row r="82" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="14"/>
-      <c r="B82" s="48">
-        <v>79</v>
-      </c>
-      <c r="C82" s="50"/>
+      <c r="B82" s="15">
+        <v>78</v>
+      </c>
+      <c r="C82" s="3"/>
       <c r="D82" s="18"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="20"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="17"/>
       <c r="G82" s="17"/>
       <c r="H82" s="17"/>
       <c r="I82" s="2"/>
@@ -6262,13 +6501,13 @@
     </row>
     <row r="83" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="14"/>
-      <c r="B83" s="15">
-        <v>80</v>
+      <c r="B83" s="48">
+        <v>79</v>
       </c>
       <c r="C83" s="50"/>
       <c r="D83" s="18"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="17"/>
+      <c r="E83" s="51"/>
+      <c r="F83" s="20"/>
       <c r="G83" s="17"/>
       <c r="H83" s="17"/>
       <c r="I83" s="2"/>
@@ -6277,7 +6516,7 @@
     <row r="84" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="14"/>
       <c r="B84" s="15">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C84" s="50"/>
       <c r="D84" s="18"/>
@@ -6291,7 +6530,7 @@
     <row r="85" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="14"/>
       <c r="B85" s="15">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C85" s="50"/>
       <c r="D85" s="18"/>
@@ -6305,7 +6544,7 @@
     <row r="86" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="14"/>
       <c r="B86" s="15">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C86" s="50"/>
       <c r="D86" s="18"/>
@@ -6319,9 +6558,9 @@
     <row r="87" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="14"/>
       <c r="B87" s="15">
-        <v>84</v>
-      </c>
-      <c r="C87" s="15"/>
+        <v>83</v>
+      </c>
+      <c r="C87" s="50"/>
       <c r="D87" s="18"/>
       <c r="E87" s="16"/>
       <c r="F87" s="17"/>
@@ -6333,9 +6572,9 @@
     <row r="88" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="14"/>
       <c r="B88" s="15">
-        <v>85</v>
-      </c>
-      <c r="C88" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="C88" s="15"/>
       <c r="D88" s="18"/>
       <c r="E88" s="16"/>
       <c r="F88" s="17"/>
@@ -6347,7 +6586,7 @@
     <row r="89" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="14"/>
       <c r="B89" s="15">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C89" s="3"/>
       <c r="D89" s="18"/>
@@ -6361,7 +6600,7 @@
     <row r="90" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="14"/>
       <c r="B90" s="15">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C90" s="3"/>
       <c r="D90" s="18"/>
@@ -6375,7 +6614,7 @@
     <row r="91" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="14"/>
       <c r="B91" s="15">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="18"/>
@@ -6388,10 +6627,10 @@
     </row>
     <row r="92" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="14"/>
-      <c r="B92" s="48">
-        <v>89</v>
-      </c>
-      <c r="C92" s="37"/>
+      <c r="B92" s="15">
+        <v>88</v>
+      </c>
+      <c r="C92" s="3"/>
       <c r="D92" s="18"/>
       <c r="E92" s="16"/>
       <c r="F92" s="17"/>
@@ -6402,10 +6641,10 @@
     </row>
     <row r="93" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="14"/>
-      <c r="B93" s="15">
-        <v>90</v>
-      </c>
-      <c r="C93" s="15"/>
+      <c r="B93" s="48">
+        <v>89</v>
+      </c>
+      <c r="C93" s="37"/>
       <c r="D93" s="18"/>
       <c r="E93" s="16"/>
       <c r="F93" s="17"/>
@@ -6417,7 +6656,7 @@
     <row r="94" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="14"/>
       <c r="B94" s="15">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="18"/>
@@ -6431,7 +6670,7 @@
     <row r="95" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="14"/>
       <c r="B95" s="15">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C95" s="15"/>
       <c r="D95" s="18"/>
@@ -6445,7 +6684,7 @@
     <row r="96" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="14"/>
       <c r="B96" s="15">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C96" s="15"/>
       <c r="D96" s="18"/>
@@ -6459,7 +6698,7 @@
     <row r="97" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="14"/>
       <c r="B97" s="15">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C97" s="15"/>
       <c r="D97" s="18"/>
@@ -6473,12 +6712,12 @@
     <row r="98" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="14"/>
       <c r="B98" s="15">
-        <v>95</v>
-      </c>
-      <c r="C98" s="37"/>
+        <v>94</v>
+      </c>
+      <c r="C98" s="15"/>
       <c r="D98" s="18"/>
-      <c r="E98" s="20"/>
-      <c r="F98" s="20"/>
+      <c r="E98" s="16"/>
+      <c r="F98" s="17"/>
       <c r="G98" s="17"/>
       <c r="H98" s="17"/>
       <c r="I98" s="2"/>
@@ -6487,12 +6726,12 @@
     <row r="99" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="14"/>
       <c r="B99" s="15">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C99" s="37"/>
       <c r="D99" s="18"/>
-      <c r="E99" s="16"/>
-      <c r="F99" s="17"/>
+      <c r="E99" s="20"/>
+      <c r="F99" s="20"/>
       <c r="G99" s="17"/>
       <c r="H99" s="17"/>
       <c r="I99" s="2"/>
@@ -6501,9 +6740,9 @@
     <row r="100" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="14"/>
       <c r="B100" s="15">
-        <v>97</v>
-      </c>
-      <c r="C100" s="15"/>
+        <v>96</v>
+      </c>
+      <c r="C100" s="37"/>
       <c r="D100" s="18"/>
       <c r="E100" s="16"/>
       <c r="F100" s="17"/>
@@ -6515,7 +6754,7 @@
     <row r="101" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="14"/>
       <c r="B101" s="15">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C101" s="15"/>
       <c r="D101" s="18"/>
@@ -6529,7 +6768,7 @@
     <row r="102" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="14"/>
       <c r="B102" s="15">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C102" s="15"/>
       <c r="D102" s="18"/>
@@ -6543,7 +6782,7 @@
     <row r="103" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="14"/>
       <c r="B103" s="15">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C103" s="15"/>
       <c r="D103" s="18"/>
@@ -6557,7 +6796,7 @@
     <row r="104" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="14"/>
       <c r="B104" s="15">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C104" s="15"/>
       <c r="D104" s="18"/>
@@ -6571,7 +6810,7 @@
     <row r="105" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="14"/>
       <c r="B105" s="15">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="18"/>
@@ -6585,7 +6824,7 @@
     <row r="106" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="14"/>
       <c r="B106" s="15">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C106" s="15"/>
       <c r="D106" s="18"/>
@@ -6598,7 +6837,9 @@
     </row>
     <row r="107" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="14"/>
-      <c r="B107" s="15"/>
+      <c r="B107" s="15">
+        <v>103</v>
+      </c>
       <c r="C107" s="15"/>
       <c r="D107" s="18"/>
       <c r="E107" s="16"/>
@@ -6635,104 +6876,104 @@
       <c r="J109" s="2"/>
     </row>
     <row r="110" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" s="23"/>
-      <c r="C110" s="23"/>
-      <c r="D110" s="24"/>
-      <c r="E110" s="25">
-        <f>SUM(E3:E109)</f>
-        <v>0</v>
-      </c>
-      <c r="F110" s="26">
-        <f>SUM(F3:F109)</f>
-        <v>4709.7900000000245</v>
-      </c>
-      <c r="G110" s="26">
-        <f>SUM(G3:G109)</f>
-        <v>2000.5</v>
-      </c>
-      <c r="H110" s="26">
-        <f>SUM(H3:H109)</f>
-        <v>4633.9699999999993</v>
-      </c>
+      <c r="A110" s="14"/>
+      <c r="B110" s="15"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="18"/>
+      <c r="E110" s="16"/>
+      <c r="F110" s="17"/>
+      <c r="G110" s="17"/>
+      <c r="H110" s="17"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
     </row>
     <row r="111" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="33"/>
-      <c r="B111" s="33"/>
-      <c r="C111" s="33"/>
-      <c r="D111" s="33"/>
-      <c r="E111" s="34"/>
-      <c r="F111" s="34"/>
-      <c r="G111" s="34"/>
-      <c r="H111" s="34"/>
+      <c r="A111" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="25">
+        <f>SUM(E3:E110)</f>
+        <v>0</v>
+      </c>
+      <c r="F111" s="26">
+        <f>SUM(F3:F110)</f>
+        <v>5465.6900000000242</v>
+      </c>
+      <c r="G111" s="26">
+        <f>SUM(G3:G110)</f>
+        <v>2000.5</v>
+      </c>
+      <c r="H111" s="26">
+        <f>SUM(H3:H110)</f>
+        <v>5951.61</v>
+      </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
     </row>
     <row r="112" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B112" s="23"/>
-      <c r="C112" s="23"/>
-      <c r="D112" s="45"/>
-      <c r="E112" s="26">
-        <f>E110+Ausgaben!F178</f>
-        <v>0</v>
-      </c>
-      <c r="F112" s="26">
-        <f>F110+Ausgaben!G178</f>
-        <v>2381.1300000000247</v>
-      </c>
-      <c r="G112" s="26">
-        <f>G110+Ausgaben!H178</f>
-        <v>2000.5</v>
-      </c>
-      <c r="H112" s="26">
-        <f>H110+Ausgaben!I178</f>
-        <v>1448.0599999999995</v>
-      </c>
+      <c r="A112" s="33"/>
+      <c r="B112" s="33"/>
+      <c r="C112" s="33"/>
+      <c r="D112" s="33"/>
+      <c r="E112" s="34"/>
+      <c r="F112" s="34"/>
+      <c r="G112" s="34"/>
+      <c r="H112" s="34"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
     </row>
     <row r="113" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="35"/>
-      <c r="B113" s="35"/>
-      <c r="C113" s="35"/>
-      <c r="D113" s="35"/>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="13"/>
-      <c r="H113" s="13"/>
+      <c r="A113" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B113" s="23"/>
+      <c r="C113" s="23"/>
+      <c r="D113" s="45"/>
+      <c r="E113" s="26">
+        <f>E111+Ausgaben!F178</f>
+        <v>0</v>
+      </c>
+      <c r="F113" s="26">
+        <f>F111+Ausgaben!G178</f>
+        <v>2023.560000000025</v>
+      </c>
+      <c r="G113" s="26">
+        <f>G111+Ausgaben!H178</f>
+        <v>2000.5</v>
+      </c>
+      <c r="H113" s="26">
+        <f>H111+Ausgaben!I178</f>
+        <v>2763.2</v>
+      </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
     </row>
     <row r="114" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B114" s="5"/>
-      <c r="C114" s="22"/>
-      <c r="D114" s="27">
-        <f>SUM(E112:H112)</f>
-        <v>5829.6900000000242</v>
-      </c>
-      <c r="E114" s="16"/>
-      <c r="F114" s="17"/>
-      <c r="G114" s="17"/>
-      <c r="H114" s="17"/>
+      <c r="A114" s="35"/>
+      <c r="B114" s="35"/>
+      <c r="C114" s="35"/>
+      <c r="D114" s="35"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
     </row>
     <row r="115" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="36"/>
-      <c r="B115" s="36"/>
-      <c r="C115" s="36"/>
-      <c r="D115" s="36"/>
-      <c r="E115" s="17"/>
+      <c r="A115" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B115" s="5"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="27">
+        <f>SUM(E113:H113)</f>
+        <v>6787.2600000000248</v>
+      </c>
+      <c r="E115" s="16"/>
       <c r="F115" s="17"/>
       <c r="G115" s="17"/>
       <c r="H115" s="17"/>
@@ -6740,12 +6981,10 @@
       <c r="J115" s="2"/>
     </row>
     <row r="116" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="A116" s="36"/>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
       <c r="E116" s="17"/>
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
@@ -6757,7 +6996,9 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
+      <c r="D117" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E117" s="17"/>
       <c r="F117" s="17"/>
       <c r="G117" s="17"/>
@@ -7450,125 +7691,148 @@
       <c r="J174" s="2"/>
     </row>
     <row r="175" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="17"/>
+      <c r="F175" s="17"/>
+      <c r="G175" s="17"/>
+      <c r="H175" s="17"/>
       <c r="J175" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H106" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:H107" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B82 H4:H10 G11:H16">
-    <cfRule type="cellIs" dxfId="42" priority="198" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="C99:D100">
+    <cfRule type="cellIs" dxfId="47" priority="60" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C98:D99">
-    <cfRule type="cellIs" dxfId="41" priority="51" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 H27 H34:H110 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97 G24:H24">
+    <cfRule type="cellIs" dxfId="46" priority="65" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D82:D88">
-    <cfRule type="cellIs" dxfId="40" priority="15" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D20:D22 D29:D61">
+    <cfRule type="cellIs" dxfId="45" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D81:F81">
-    <cfRule type="cellIs" dxfId="39" priority="16" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D83:D89">
+    <cfRule type="cellIs" dxfId="44" priority="24" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D77:G80">
-    <cfRule type="cellIs" dxfId="38" priority="17" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D82:F82">
+    <cfRule type="cellIs" dxfId="43" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D100:G109">
-    <cfRule type="cellIs" dxfId="37" priority="49" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D78:G81">
+    <cfRule type="cellIs" dxfId="42" priority="26" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E23">
-    <cfRule type="cellIs" dxfId="36" priority="76" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D101:G110">
+    <cfRule type="cellIs" dxfId="41" priority="58" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E40:F41">
-    <cfRule type="cellIs" dxfId="35" priority="14" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E24">
+    <cfRule type="cellIs" dxfId="40" priority="85" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45:F45">
-    <cfRule type="cellIs" dxfId="34" priority="36" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E41:F42">
+    <cfRule type="cellIs" dxfId="39" priority="23" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E33:G39 G40:G46">
-    <cfRule type="cellIs" dxfId="33" priority="38" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E46:F46">
+    <cfRule type="cellIs" dxfId="38" priority="45" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E47:G48 G49:G50 E50:F50 F51:G51 G52:G57">
-    <cfRule type="cellIs" dxfId="32" priority="96" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E34:G40 G41:G47">
+    <cfRule type="cellIs" dxfId="37" priority="47" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E68:G70 G81:G82">
-    <cfRule type="cellIs" dxfId="31" priority="70" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E48:G49 G50:G51 E51:F51 F52:G52 G53:G58">
+    <cfRule type="cellIs" dxfId="36" priority="105" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E83:G88 D89:G97">
-    <cfRule type="cellIs" dxfId="30" priority="52" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E69:G71 G82:G83">
+    <cfRule type="cellIs" dxfId="35" priority="79" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3 G98 E99:G99 D109:H109 E110:H174 D114">
-    <cfRule type="cellIs" dxfId="29" priority="350" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E84:G89 D90:G98">
+    <cfRule type="cellIs" dxfId="34" priority="61" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24:G24">
-    <cfRule type="cellIs" dxfId="28" priority="271" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E3:H3">
+    <cfRule type="cellIs" dxfId="33" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F58:G59">
-    <cfRule type="cellIs" dxfId="27" priority="13" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F25:G25">
+    <cfRule type="cellIs" dxfId="32" priority="280" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F71:G71">
-    <cfRule type="cellIs" dxfId="26" priority="68" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F59:G60">
+    <cfRule type="cellIs" dxfId="31" priority="22" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G13 A92:C92">
-    <cfRule type="cellIs" dxfId="25" priority="184" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="F72:G72">
+    <cfRule type="cellIs" dxfId="30" priority="77" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G25:G26">
-    <cfRule type="cellIs" dxfId="24" priority="268" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G4:G13 A93:C93">
+    <cfRule type="cellIs" dxfId="29" priority="193" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G27:H32">
-    <cfRule type="cellIs" dxfId="23" priority="45" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G26:G27">
+    <cfRule type="cellIs" dxfId="28" priority="277" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G21:G23 H21:H26 D21:D60 H33:H109 E53:F57 D60:G67 D68:D76 E72:G76 A93:A96">
-    <cfRule type="cellIs" dxfId="22" priority="56" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
+    <cfRule type="cellIs" dxfId="27" priority="359" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:H3">
-    <cfRule type="cellIs" dxfId="21" priority="1" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G11:H22">
+    <cfRule type="cellIs" dxfId="26" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28:H33">
+    <cfRule type="cellIs" dxfId="25" priority="54" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H10 B83">
+    <cfRule type="cellIs" dxfId="24" priority="207" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H26">
+    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D21:D109" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D110" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$J$1:$J$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -7608,16 +7872,16 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="39"/>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
       <c r="J1" s="4"/>
       <c r="K1" s="2"/>
       <c r="L1" s="3" t="s">
@@ -8602,14 +8866,22 @@
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="41"/>
-      <c r="B41" s="14"/>
+      <c r="B41" s="14">
+        <v>46104</v>
+      </c>
       <c r="C41" s="48">
         <v>37</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="82"/>
+      <c r="D41" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F41" s="19"/>
-      <c r="G41" s="20"/>
+      <c r="G41" s="20">
+        <v>-105</v>
+      </c>
       <c r="H41" s="20"/>
       <c r="I41" s="20"/>
       <c r="J41" s="4"/>
@@ -8618,14 +8890,22 @@
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="41"/>
-      <c r="B42" s="14"/>
+      <c r="B42" s="14">
+        <v>46106</v>
+      </c>
       <c r="C42" s="48">
         <v>38</v>
       </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="82"/>
+      <c r="D42" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F42" s="19"/>
-      <c r="G42" s="20"/>
+      <c r="G42" s="20">
+        <v>-4.99</v>
+      </c>
       <c r="H42" s="20"/>
       <c r="I42" s="20"/>
       <c r="J42" s="4"/>
@@ -8634,14 +8914,22 @@
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="41"/>
-      <c r="B43" s="14"/>
+      <c r="B43" s="14">
+        <v>46106</v>
+      </c>
       <c r="C43" s="48">
         <v>39</v>
       </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="82"/>
+      <c r="D43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F43" s="19"/>
-      <c r="G43" s="20"/>
+      <c r="G43" s="20">
+        <v>-15</v>
+      </c>
       <c r="H43" s="20"/>
       <c r="I43" s="20"/>
       <c r="J43" s="4"/>
@@ -8650,14 +8938,22 @@
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="41"/>
-      <c r="B44" s="14"/>
+      <c r="B44" s="14">
+        <v>46106</v>
+      </c>
       <c r="C44" s="48">
         <v>40</v>
       </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="82"/>
+      <c r="D44" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F44" s="19"/>
-      <c r="G44" s="20"/>
+      <c r="G44" s="20">
+        <v>-56.83</v>
+      </c>
       <c r="H44" s="20"/>
       <c r="I44" s="20"/>
       <c r="J44" s="4"/>
@@ -8666,14 +8962,22 @@
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="41"/>
-      <c r="B45" s="14"/>
+      <c r="B45" s="14">
+        <v>46108</v>
+      </c>
       <c r="C45" s="48">
         <v>41</v>
       </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="82"/>
+      <c r="D45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F45" s="19"/>
-      <c r="G45" s="20"/>
+      <c r="G45" s="20">
+        <v>-153</v>
+      </c>
       <c r="H45" s="20"/>
       <c r="I45" s="20"/>
       <c r="J45" s="4"/>
@@ -8682,30 +8986,46 @@
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="41"/>
-      <c r="B46" s="14"/>
+      <c r="B46" s="14">
+        <v>46108</v>
+      </c>
       <c r="C46" s="48">
         <v>42</v>
       </c>
-      <c r="D46" s="3"/>
-      <c r="E46" s="82"/>
+      <c r="D46" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F46" s="19"/>
       <c r="G46" s="20"/>
       <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
+      <c r="I46" s="20">
+        <v>0</v>
+      </c>
       <c r="J46" s="4"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="41"/>
-      <c r="B47" s="14"/>
+      <c r="B47" s="14">
+        <v>46111</v>
+      </c>
       <c r="C47" s="48">
         <v>43</v>
       </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="82"/>
+      <c r="D47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F47" s="19"/>
-      <c r="G47" s="20"/>
+      <c r="G47" s="20">
+        <v>-9.77</v>
+      </c>
       <c r="H47" s="20"/>
       <c r="I47" s="20"/>
       <c r="J47" s="4"/>
@@ -8714,14 +9034,22 @@
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="41"/>
-      <c r="B48" s="14"/>
+      <c r="B48" s="14">
+        <v>46111</v>
+      </c>
       <c r="C48" s="48">
         <v>44</v>
       </c>
-      <c r="D48" s="81"/>
-      <c r="E48" s="82"/>
+      <c r="D48" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F48" s="19"/>
-      <c r="G48" s="20"/>
+      <c r="G48" s="20">
+        <v>-108</v>
+      </c>
       <c r="H48" s="20"/>
       <c r="I48" s="20"/>
       <c r="J48" s="4"/>
@@ -8730,14 +9058,22 @@
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="41"/>
-      <c r="B49" s="14"/>
+      <c r="B49" s="14">
+        <v>46111</v>
+      </c>
       <c r="C49" s="48">
         <v>45</v>
       </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="82"/>
+      <c r="D49" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F49" s="19"/>
-      <c r="G49" s="20"/>
+      <c r="G49" s="20">
+        <v>-48.94</v>
+      </c>
       <c r="H49" s="20"/>
       <c r="I49" s="20"/>
       <c r="J49" s="4"/>
@@ -8746,14 +9082,22 @@
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="41"/>
-      <c r="B50" s="14"/>
+      <c r="B50" s="14">
+        <v>46111</v>
+      </c>
       <c r="C50" s="48">
         <v>46</v>
       </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="82"/>
+      <c r="D50" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F50" s="19"/>
-      <c r="G50" s="20"/>
+      <c r="G50" s="20">
+        <v>-78.349999999999994</v>
+      </c>
       <c r="H50" s="20"/>
       <c r="I50" s="20"/>
       <c r="J50" s="4"/>
@@ -8762,14 +9106,22 @@
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="41"/>
-      <c r="B51" s="14"/>
+      <c r="B51" s="14">
+        <v>46111</v>
+      </c>
       <c r="C51" s="48">
         <v>47</v>
       </c>
-      <c r="D51" s="3"/>
-      <c r="E51" s="82"/>
+      <c r="D51" s="81" t="s">
+        <v>94</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F51" s="19"/>
-      <c r="G51" s="20"/>
+      <c r="G51" s="20">
+        <v>-70.680000000000007</v>
+      </c>
       <c r="H51" s="20"/>
       <c r="I51" s="20"/>
       <c r="J51" s="4"/>
@@ -8778,14 +9130,22 @@
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="41"/>
-      <c r="B52" s="14"/>
+      <c r="B52" s="14">
+        <v>46111</v>
+      </c>
       <c r="C52" s="48">
         <v>48</v>
       </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="82"/>
+      <c r="D52" s="81" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F52" s="19"/>
-      <c r="G52" s="20"/>
+      <c r="G52" s="20">
+        <v>-246.8</v>
+      </c>
       <c r="H52" s="20"/>
       <c r="I52" s="20"/>
       <c r="J52" s="4"/>
@@ -8794,14 +9154,22 @@
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="41"/>
-      <c r="B53" s="14"/>
+      <c r="B53" s="14">
+        <v>46111</v>
+      </c>
       <c r="C53" s="48">
         <v>49</v>
       </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="82"/>
+      <c r="D53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F53" s="19"/>
-      <c r="G53" s="20"/>
+      <c r="G53" s="20">
+        <v>-9.64</v>
+      </c>
       <c r="H53" s="20"/>
       <c r="I53" s="20"/>
       <c r="J53" s="4"/>
@@ -8810,14 +9178,22 @@
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="41"/>
-      <c r="B54" s="14"/>
+      <c r="B54" s="14">
+        <v>46111</v>
+      </c>
       <c r="C54" s="48">
         <v>50</v>
       </c>
-      <c r="D54" s="37"/>
-      <c r="E54" s="18"/>
+      <c r="D54" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
+      <c r="G54" s="20">
+        <v>-25</v>
+      </c>
       <c r="H54" s="20"/>
       <c r="I54" s="20"/>
       <c r="J54" s="4"/>
@@ -8826,30 +9202,46 @@
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="41"/>
-      <c r="B55" s="14"/>
+      <c r="B55" s="14">
+        <v>46112</v>
+      </c>
       <c r="C55" s="48">
         <v>51</v>
       </c>
-      <c r="D55" s="3"/>
-      <c r="E55" s="82"/>
+      <c r="D55" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F55" s="19"/>
       <c r="G55" s="20"/>
       <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
+      <c r="I55" s="20">
+        <v>-2.5</v>
+      </c>
       <c r="J55" s="4"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="41"/>
-      <c r="B56" s="14"/>
+      <c r="B56" s="14">
+        <v>46113</v>
+      </c>
       <c r="C56" s="48">
         <v>52</v>
       </c>
-      <c r="D56" s="3"/>
-      <c r="E56" s="21"/>
+      <c r="D56" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="F56" s="19"/>
-      <c r="G56" s="20"/>
+      <c r="G56" s="20">
+        <v>-12</v>
+      </c>
       <c r="H56" s="20"/>
       <c r="I56" s="20"/>
       <c r="J56" s="4"/>
@@ -8858,14 +9250,22 @@
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="41"/>
-      <c r="B57" s="14"/>
+      <c r="B57" s="14">
+        <v>46113</v>
+      </c>
       <c r="C57" s="48">
         <v>53</v>
       </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="82"/>
+      <c r="D57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F57" s="19"/>
-      <c r="G57" s="20"/>
+      <c r="G57" s="20">
+        <v>-22</v>
+      </c>
       <c r="H57" s="20"/>
       <c r="I57" s="20"/>
       <c r="J57" s="4"/>
@@ -8874,14 +9274,22 @@
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="41"/>
-      <c r="B58" s="14"/>
+      <c r="B58" s="14">
+        <v>46114</v>
+      </c>
       <c r="C58" s="48">
         <v>54</v>
       </c>
-      <c r="D58" s="3"/>
-      <c r="E58" s="82"/>
+      <c r="D58" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="E58" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F58" s="19"/>
-      <c r="G58" s="20"/>
+      <c r="G58" s="20">
+        <v>-47</v>
+      </c>
       <c r="H58" s="20"/>
       <c r="I58" s="20"/>
       <c r="J58" s="4"/>
@@ -8890,14 +9298,22 @@
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="41"/>
-      <c r="B59" s="14"/>
+      <c r="B59" s="14">
+        <v>46114</v>
+      </c>
       <c r="C59" s="48">
         <v>55</v>
       </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="82"/>
+      <c r="D59" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F59" s="19"/>
-      <c r="G59" s="20"/>
+      <c r="G59" s="20">
+        <v>-89</v>
+      </c>
       <c r="H59" s="20"/>
       <c r="I59" s="20"/>
       <c r="J59" s="4"/>
@@ -8906,14 +9322,22 @@
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="41"/>
-      <c r="B60" s="14"/>
+      <c r="B60" s="14">
+        <v>46119</v>
+      </c>
       <c r="C60" s="48">
         <v>56</v>
       </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="82"/>
+      <c r="D60" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F60" s="19"/>
-      <c r="G60" s="20"/>
+      <c r="G60" s="20">
+        <v>-11.47</v>
+      </c>
       <c r="H60" s="20"/>
       <c r="I60" s="20"/>
       <c r="J60" s="4"/>
@@ -10806,7 +11230,7 @@
       </c>
       <c r="G178" s="32">
         <f>SUM(G3:G177)</f>
-        <v>-2328.66</v>
+        <v>-3442.1299999999992</v>
       </c>
       <c r="H178" s="32">
         <f>SUM(H3:H177)</f>
@@ -10814,7 +11238,7 @@
       </c>
       <c r="I178" s="32">
         <f>SUM(I3:I177)</f>
-        <v>-3185.91</v>
+        <v>-3188.41</v>
       </c>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
@@ -11727,116 +12151,123 @@
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A242 E33 E41:E123 E133:E144">
-    <cfRule type="cellIs" dxfId="20" priority="484" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A3:A242 E33 E61:E123 E133:E144">
+    <cfRule type="cellIs" dxfId="23" priority="486" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129:B142">
-    <cfRule type="cellIs" dxfId="19" priority="467" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="469" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156:B244">
-    <cfRule type="cellIs" dxfId="18" priority="24" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="26" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C155 C157 C159 C161 C163 C165 C167 C173 C175">
-    <cfRule type="cellIs" dxfId="17" priority="25" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C243 J179 I179:I244">
-    <cfRule type="cellIs" dxfId="16" priority="714" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="716" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D132">
-    <cfRule type="cellIs" dxfId="15" priority="482" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="484" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D149">
-    <cfRule type="cellIs" dxfId="14" priority="69" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="71" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D153:D154">
-    <cfRule type="cellIs" dxfId="13" priority="453" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="455" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D158:D163">
-    <cfRule type="cellIs" dxfId="12" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:E165 D166:D167 C169:D169 D170:E170 C171:D171">
-    <cfRule type="cellIs" dxfId="11" priority="17" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="19" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D177:E179">
-    <cfRule type="cellIs" dxfId="10" priority="19" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="21" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D179:H242">
-    <cfRule type="cellIs" dxfId="9" priority="666" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="668" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E125:E131 E146:E163">
-    <cfRule type="cellIs" dxfId="8" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="7" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:E20">
+    <cfRule type="cellIs" dxfId="10" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="4" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E42">
+    <cfRule type="cellIs" dxfId="8" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E169">
-    <cfRule type="cellIs" dxfId="6" priority="7" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="9" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:E176">
-    <cfRule type="cellIs" dxfId="5" priority="6" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="cellIs" dxfId="4" priority="375" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="377" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="cellIs" dxfId="2" priority="127" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="129" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="cellIs" dxfId="1" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E19:E20">
+  <conditionalFormatting sqref="E58:E59">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E54" xr:uid="{2159CF4B-2649-4586-B851-DB145DFC2247}">
-      <formula1>$J$1:$J$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E55:E123 E41:E53 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E146:E177 E125:E131 E133:E144 E19:E20" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E146:E177 E125:E131 E133:E144 E58:E59 E61:E123" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$L$1:$L$19</formula1>
     </dataValidation>
   </dataValidations>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BAC7CC-296D-4AD9-8E58-A65DAF98D7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB85F5B5-28AC-4A29-ADD4-B2C70932E79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="103">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -336,7 +336,13 @@
     <t>Awo Open</t>
   </si>
   <si>
-    <t xml:space="preserve">Awo Einlage Kreis </t>
+    <t>Awo Kreis Zinsen Kapitalfond</t>
+  </si>
+  <si>
+    <t>AWO Bund Rückverteilung</t>
+  </si>
+  <si>
+    <t>Spende JHV H.Heimann</t>
   </si>
 </sst>
 </file>
@@ -5749,37 +5755,57 @@
       <c r="C29" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="18"/>
+      <c r="D29" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="E29" s="19"/>
-      <c r="F29" s="20"/>
+      <c r="F29" s="20">
+        <v>250</v>
+      </c>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
+      <c r="A30" s="14">
+        <v>46121</v>
+      </c>
       <c r="B30" s="15">
         <v>26</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="18"/>
+      <c r="C30" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E30" s="19"/>
-      <c r="F30" s="20"/>
+      <c r="F30" s="20">
+        <v>22.19</v>
+      </c>
       <c r="G30" s="17"/>
       <c r="H30" s="17"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
+      <c r="A31" s="14">
+        <v>46121</v>
+      </c>
       <c r="B31" s="15">
         <v>27</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="18"/>
+      <c r="C31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>12</v>
+      </c>
       <c r="E31" s="19"/>
-      <c r="F31" s="20"/>
+      <c r="F31" s="20">
+        <v>50</v>
+      </c>
       <c r="G31" s="17"/>
       <c r="H31" s="17"/>
       <c r="I31" s="2"/>
@@ -6900,7 +6926,7 @@
       </c>
       <c r="F111" s="26">
         <f>SUM(F3:F110)</f>
-        <v>5465.6900000000242</v>
+        <v>5787.8800000000238</v>
       </c>
       <c r="G111" s="26">
         <f>SUM(G3:G110)</f>
@@ -6938,7 +6964,7 @@
       </c>
       <c r="F113" s="26">
         <f>F111+Ausgaben!G178</f>
-        <v>2023.560000000025</v>
+        <v>2345.7500000000246</v>
       </c>
       <c r="G113" s="26">
         <f>G111+Ausgaben!H178</f>
@@ -6971,7 +6997,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>6787.2600000000248</v>
+        <v>7109.4500000000244</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -7711,12 +7737,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6 D8:D9 D11:D14 H27 H34:H110 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97 G24:H24">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 H34:H110 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97">
     <cfRule type="cellIs" dxfId="46" priority="65" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D29:D61">
+  <conditionalFormatting sqref="D20:D22 D31:D61">
     <cfRule type="cellIs" dxfId="45" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -7826,13 +7852,13 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H26">
-    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="H25:H27">
+    <cfRule type="cellIs" dxfId="23" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D110" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 D6 D8:D9 D11:D14 D17:D22 D24:D28 D31:D110" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$J$1:$J$19</formula1>
     </dataValidation>
   </dataValidations>
@@ -12152,117 +12178,117 @@
     <mergeCell ref="B1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:A242 E33 E61:E123 E133:E144">
-    <cfRule type="cellIs" dxfId="23" priority="486" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="486" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129:B142">
-    <cfRule type="cellIs" dxfId="22" priority="469" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="469" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156:B244">
-    <cfRule type="cellIs" dxfId="21" priority="26" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="26" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C155 C157 C159 C161 C163 C165 C167 C173 C175">
-    <cfRule type="cellIs" dxfId="20" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="27" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C243 J179 I179:I244">
-    <cfRule type="cellIs" dxfId="19" priority="716" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="716" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D132">
-    <cfRule type="cellIs" dxfId="18" priority="484" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="484" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D149">
-    <cfRule type="cellIs" dxfId="17" priority="71" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="71" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D153:D154">
-    <cfRule type="cellIs" dxfId="16" priority="455" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="455" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D158:D163">
-    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:E165 D166:D167 C169:D169 D170:E170 C171:D171">
-    <cfRule type="cellIs" dxfId="14" priority="19" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="19" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D177:E179">
-    <cfRule type="cellIs" dxfId="13" priority="21" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="21" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D179:H242">
-    <cfRule type="cellIs" dxfId="12" priority="668" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="668" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E125:E131 E146:E163">
-    <cfRule type="cellIs" dxfId="11" priority="7" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="10" priority="3" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="9" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="8" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E58:E59">
+    <cfRule type="cellIs" dxfId="6" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E169">
-    <cfRule type="cellIs" dxfId="7" priority="9" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="9" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:E176">
-    <cfRule type="cellIs" dxfId="6" priority="8" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64:F65">
-    <cfRule type="cellIs" dxfId="5" priority="377" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="377" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="4" priority="6" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="cellIs" dxfId="3" priority="129" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="129" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E58:E59">
-    <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB85F5B5-28AC-4A29-ADD4-B2C70932E79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88538749-59E3-4FA4-B143-D088EAB24873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="107">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -343,6 +343,18 @@
   </si>
   <si>
     <t>Spende JHV H.Heimann</t>
+  </si>
+  <si>
+    <t>Abschluss KSK siehe Ktauszug04</t>
+  </si>
+  <si>
+    <t>Bargeldeinzahlung 90 Günne Senioren+100tzgl+140busreise</t>
+  </si>
+  <si>
+    <t>Radservice Spendenbox</t>
+  </si>
+  <si>
+    <t>Radservice Brezeln</t>
   </si>
 </sst>
 </file>
@@ -1018,7 +1030,27 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="54">
+  <dxfs count="58">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -3829,17 +3861,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="50">
+    <format dxfId="54">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3943,17 +3975,17 @@
     <dataField name="Summe von KSK SpB 3001734183" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="53">
+    <format dxfId="57">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -5812,28 +5844,44 @@
       <c r="J31" s="2"/>
     </row>
     <row r="32" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
+      <c r="A32" s="14">
+        <v>46129</v>
+      </c>
       <c r="B32" s="15">
         <v>28</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="20"/>
+      <c r="C32" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="17"/>
       <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
+      <c r="H32" s="17">
+        <v>330</v>
+      </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
+      <c r="A33" s="14">
+        <v>46139</v>
+      </c>
       <c r="B33" s="15">
         <v>29</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="18"/>
+      <c r="C33" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E33" s="19"/>
-      <c r="F33" s="20"/>
+      <c r="F33" s="20">
+        <v>128.5</v>
+      </c>
       <c r="G33" s="17"/>
       <c r="H33" s="17"/>
       <c r="I33" s="2"/>
@@ -6926,7 +6974,7 @@
       </c>
       <c r="F111" s="26">
         <f>SUM(F3:F110)</f>
-        <v>5787.8800000000238</v>
+        <v>5916.3800000000238</v>
       </c>
       <c r="G111" s="26">
         <f>SUM(G3:G110)</f>
@@ -6934,7 +6982,7 @@
       </c>
       <c r="H111" s="26">
         <f>SUM(H3:H110)</f>
-        <v>5951.61</v>
+        <v>6281.61</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -6964,7 +7012,7 @@
       </c>
       <c r="F113" s="26">
         <f>F111+Ausgaben!G178</f>
-        <v>2345.7500000000246</v>
+        <v>2411.8500000000249</v>
       </c>
       <c r="G113" s="26">
         <f>G111+Ausgaben!H178</f>
@@ -6972,7 +7020,7 @@
       </c>
       <c r="H113" s="26">
         <f>H111+Ausgaben!I178</f>
-        <v>2763.2</v>
+        <v>3085.7</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
@@ -6997,7 +7045,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>7109.4500000000244</v>
+        <v>7498.0500000000247</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -7733,127 +7781,137 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="C99:D100">
-    <cfRule type="cellIs" dxfId="47" priority="60" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="51" priority="62" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 H34:H110 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97">
-    <cfRule type="cellIs" dxfId="46" priority="65" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="50" priority="67" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D31:D61">
-    <cfRule type="cellIs" dxfId="45" priority="3" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="D20:D22 D31 D34:D61">
+    <cfRule type="cellIs" dxfId="49" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D83:D89">
-    <cfRule type="cellIs" dxfId="44" priority="24" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="48" priority="26" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D82:F82">
+    <cfRule type="cellIs" dxfId="47" priority="27" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D78:G81">
+    <cfRule type="cellIs" dxfId="46" priority="28" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D101:G110">
+    <cfRule type="cellIs" dxfId="45" priority="60" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24">
+    <cfRule type="cellIs" dxfId="44" priority="87" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41:F42">
     <cfRule type="cellIs" dxfId="43" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D78:G81">
-    <cfRule type="cellIs" dxfId="42" priority="26" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D101:G110">
-    <cfRule type="cellIs" dxfId="41" priority="58" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="40" priority="85" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E41:F42">
-    <cfRule type="cellIs" dxfId="39" priority="23" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="E46:F46">
-    <cfRule type="cellIs" dxfId="38" priority="45" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="47" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34:G40 G41:G47">
-    <cfRule type="cellIs" dxfId="37" priority="47" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="49" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48:G49 G50:G51 E51:F51 F52:G52 G53:G58">
-    <cfRule type="cellIs" dxfId="36" priority="105" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="107" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E69:G71 G82:G83">
-    <cfRule type="cellIs" dxfId="35" priority="79" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="81" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E84:G89 D90:G98">
-    <cfRule type="cellIs" dxfId="34" priority="61" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="63" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:H3">
-    <cfRule type="cellIs" dxfId="33" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25:G25">
-    <cfRule type="cellIs" dxfId="32" priority="280" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="36" priority="282" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:G60">
-    <cfRule type="cellIs" dxfId="31" priority="22" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="24" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72:G72">
-    <cfRule type="cellIs" dxfId="30" priority="77" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="79" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A93:C93">
-    <cfRule type="cellIs" dxfId="29" priority="193" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="195" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="cellIs" dxfId="28" priority="277" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="279" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
-    <cfRule type="cellIs" dxfId="27" priority="359" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="361" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H22">
-    <cfRule type="cellIs" dxfId="26" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28:H33">
-    <cfRule type="cellIs" dxfId="25" priority="54" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="G28:H31 G33:H33">
+    <cfRule type="cellIs" dxfId="29" priority="56" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10 B83">
-    <cfRule type="cellIs" dxfId="24" priority="207" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="209" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H27">
-    <cfRule type="cellIs" dxfId="23" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="3" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H32">
+    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32:G32">
+    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9372,14 +9430,22 @@
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="41"/>
-      <c r="B61" s="14"/>
+      <c r="B61" s="14">
+        <v>46127</v>
+      </c>
       <c r="C61" s="48">
         <v>57</v>
       </c>
-      <c r="D61" s="81"/>
-      <c r="E61" s="82"/>
+      <c r="D61" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E61" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F61" s="19"/>
-      <c r="G61" s="20"/>
+      <c r="G61" s="20">
+        <v>-18.36</v>
+      </c>
       <c r="H61" s="20"/>
       <c r="I61" s="20"/>
       <c r="J61" s="4"/>
@@ -9388,14 +9454,22 @@
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="41"/>
-      <c r="B62" s="14"/>
+      <c r="B62" s="14">
+        <v>46132</v>
+      </c>
       <c r="C62" s="48">
         <v>58</v>
       </c>
-      <c r="D62" s="3"/>
-      <c r="E62" s="82"/>
+      <c r="D62" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F62" s="19"/>
-      <c r="G62" s="20"/>
+      <c r="G62" s="20">
+        <v>-19.45</v>
+      </c>
       <c r="H62" s="20"/>
       <c r="I62" s="20"/>
       <c r="J62" s="4"/>
@@ -9404,14 +9478,22 @@
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="41"/>
-      <c r="B63" s="14"/>
+      <c r="B63" s="14">
+        <v>46139</v>
+      </c>
       <c r="C63" s="48">
         <v>59</v>
       </c>
-      <c r="D63" s="3"/>
-      <c r="E63" s="82"/>
+      <c r="D63" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F63" s="19"/>
-      <c r="G63" s="20"/>
+      <c r="G63" s="20">
+        <v>-19.600000000000001</v>
+      </c>
       <c r="H63" s="20"/>
       <c r="I63" s="20"/>
       <c r="J63" s="4"/>
@@ -9420,14 +9502,22 @@
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="41"/>
-      <c r="B64" s="14"/>
+      <c r="B64" s="14">
+        <v>46139</v>
+      </c>
       <c r="C64" s="48">
         <v>60</v>
       </c>
-      <c r="D64" s="3"/>
-      <c r="E64" s="82"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="20"/>
+      <c r="D64" s="81" t="s">
+        <v>55</v>
+      </c>
+      <c r="E64" s="82" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="19"/>
+      <c r="G64" s="20">
+        <v>-4.99</v>
+      </c>
       <c r="H64" s="20"/>
       <c r="I64" s="20"/>
       <c r="J64" s="4"/>
@@ -9436,16 +9526,24 @@
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="41"/>
-      <c r="B65" s="14"/>
+      <c r="B65" s="14">
+        <v>46142</v>
+      </c>
       <c r="C65" s="48">
         <v>61</v>
       </c>
-      <c r="D65" s="3"/>
-      <c r="E65" s="82"/>
-      <c r="F65" s="16"/>
+      <c r="D65" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="19"/>
       <c r="G65" s="20"/>
       <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
+      <c r="I65" s="20">
+        <v>-7.5</v>
+      </c>
       <c r="J65" s="4"/>
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
@@ -9585,7 +9683,7 @@
         <v>70</v>
       </c>
       <c r="D74" s="3"/>
-      <c r="E74" s="82"/>
+      <c r="E74" s="3"/>
       <c r="F74" s="19"/>
       <c r="G74" s="20"/>
       <c r="H74" s="20"/>
@@ -11256,7 +11354,7 @@
       </c>
       <c r="G178" s="32">
         <f>SUM(G3:G177)</f>
-        <v>-3442.1299999999992</v>
+        <v>-3504.5299999999988</v>
       </c>
       <c r="H178" s="32">
         <f>SUM(H3:H177)</f>
@@ -11264,7 +11362,7 @@
       </c>
       <c r="I178" s="32">
         <f>SUM(I3:I177)</f>
-        <v>-3188.41</v>
+        <v>-3195.91</v>
       </c>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
@@ -12177,123 +12275,128 @@
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A242 E33 E61:E123 E133:E144">
-    <cfRule type="cellIs" dxfId="22" priority="486" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A3:A242 E33 E66:E73 E133:E144 E75:E123">
+    <cfRule type="cellIs" dxfId="26" priority="488" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129:B142">
-    <cfRule type="cellIs" dxfId="21" priority="469" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="471" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156:B244">
-    <cfRule type="cellIs" dxfId="20" priority="26" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="28" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C155 C157 C159 C161 C163 C165 C167 C173 C175">
-    <cfRule type="cellIs" dxfId="19" priority="27" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="29" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C243 J179 I179:I244">
-    <cfRule type="cellIs" dxfId="18" priority="716" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="718" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D132">
-    <cfRule type="cellIs" dxfId="17" priority="484" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="486" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D149">
-    <cfRule type="cellIs" dxfId="16" priority="71" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="73" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D153:D154">
-    <cfRule type="cellIs" dxfId="15" priority="455" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="457" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D158:D163">
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="14" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:E165 D166:D167 C169:D169 D170:E170 C171:D171">
-    <cfRule type="cellIs" dxfId="13" priority="19" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="21" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D177:E179">
-    <cfRule type="cellIs" dxfId="12" priority="21" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="23" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D179:H242">
-    <cfRule type="cellIs" dxfId="11" priority="668" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="670" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E125:E131 E146:E163">
-    <cfRule type="cellIs" dxfId="10" priority="7" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="9" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="9" priority="3" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="8" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58:E59">
-    <cfRule type="cellIs" dxfId="6" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E169">
-    <cfRule type="cellIs" dxfId="5" priority="9" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:E176">
-    <cfRule type="cellIs" dxfId="4" priority="8" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F64:F65">
-    <cfRule type="cellIs" dxfId="3" priority="377" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="2" priority="6" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="cellIs" dxfId="1" priority="129" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="131" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="cellIs" dxfId="0" priority="13" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="15" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61">
+    <cfRule type="cellIs" dxfId="3" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E64">
+    <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E146:E177 E125:E131 E133:E144 E58:E59 E61:E123" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E146:E177 E125:E131 E133:E144 E58:E59 E75:E123 E61 E64 E66:E73" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$L$1:$L$19</formula1>
     </dataValidation>
   </dataValidations>

--- a/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
+++ b/2026/AWO_Einnahmen_Ausgaben_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubDesktopFiles\AWO\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88538749-59E3-4FA4-B143-D088EAB24873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAFDCBB-0694-465D-AD5D-69B5BE080E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="114">
   <si>
     <t>T. z. g. Laune</t>
   </si>
@@ -355,6 +355,27 @@
   </si>
   <si>
     <t>Radservice Brezeln</t>
+  </si>
+  <si>
+    <t>2.Spende Radservice2026</t>
+  </si>
+  <si>
+    <t>SPD Miete</t>
+  </si>
+  <si>
+    <t>Tinte 83,39+  tzgl 5,99</t>
+  </si>
+  <si>
+    <t>Wasser</t>
+  </si>
+  <si>
+    <t>SPD Getränke 6.5.</t>
+  </si>
+  <si>
+    <t>SPD Miete 6.5.</t>
+  </si>
+  <si>
+    <t>Spende Muttertagsbasteln</t>
   </si>
 </sst>
 </file>
@@ -5888,98 +5909,153 @@
       <c r="J33" s="2"/>
     </row>
     <row r="34" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="14"/>
+      <c r="A34" s="14">
+        <v>46146</v>
+      </c>
       <c r="B34" s="15">
         <v>30</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="18"/>
+      <c r="C34" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E34" s="16"/>
       <c r="F34" s="17"/>
       <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
+      <c r="H34" s="17">
+        <v>100</v>
+      </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
+      <c r="A35" s="14">
+        <v>46146</v>
+      </c>
       <c r="B35" s="15">
         <v>31</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="18"/>
+      <c r="C35" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E35" s="16"/>
       <c r="F35" s="17"/>
       <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
+      <c r="H35" s="17">
+        <v>10</v>
+      </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
     </row>
     <row r="36" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="14"/>
+      <c r="A36" s="14">
+        <v>46146</v>
+      </c>
       <c r="B36" s="15">
         <v>32</v>
       </c>
-      <c r="C36" s="15"/>
-      <c r="D36" s="18"/>
+      <c r="C36" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E36" s="16"/>
       <c r="F36" s="17"/>
       <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
+      <c r="H36" s="17">
+        <v>42.5</v>
+      </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
     </row>
     <row r="37" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14"/>
+      <c r="A37" s="14">
+        <v>46146</v>
+      </c>
       <c r="B37" s="15">
         <v>33</v>
       </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="18"/>
+      <c r="C37" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E37" s="16"/>
       <c r="F37" s="17"/>
       <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
+      <c r="H37" s="17">
+        <v>20</v>
+      </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
     </row>
     <row r="38" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="14"/>
+      <c r="A38" s="14">
+        <v>46150</v>
+      </c>
       <c r="B38" s="15">
         <v>34</v>
       </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="17"/>
+      <c r="C38" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19"/>
       <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
+      <c r="H38" s="20">
+        <v>28</v>
+      </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
     </row>
     <row r="39" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="14"/>
+      <c r="A39" s="14">
+        <v>46153</v>
+      </c>
       <c r="B39" s="48">
         <v>35</v>
       </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="18"/>
+      <c r="C39" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E39" s="16"/>
       <c r="F39" s="17"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
+      <c r="H39" s="17">
+        <v>20</v>
+      </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
     </row>
     <row r="40" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="14"/>
+      <c r="A40" s="14">
+        <v>46160</v>
+      </c>
       <c r="B40" s="15">
         <v>36</v>
       </c>
-      <c r="C40" s="37"/>
-      <c r="D40" s="18"/>
+      <c r="C40" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="E40" s="16"/>
-      <c r="F40" s="17"/>
+      <c r="F40" s="17">
+        <v>30</v>
+      </c>
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="2"/>
@@ -6098,7 +6174,6 @@
       <c r="J48" s="2"/>
     </row>
     <row r="49" spans="1:10" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="14"/>
       <c r="B49" s="15">
         <v>45</v>
       </c>
@@ -6974,7 +7049,7 @@
       </c>
       <c r="F111" s="26">
         <f>SUM(F3:F110)</f>
-        <v>5916.3800000000238</v>
+        <v>5946.3800000000238</v>
       </c>
       <c r="G111" s="26">
         <f>SUM(G3:G110)</f>
@@ -6982,7 +7057,7 @@
       </c>
       <c r="H111" s="26">
         <f>SUM(H3:H110)</f>
-        <v>6281.61</v>
+        <v>6502.11</v>
       </c>
       <c r="I111" s="2"/>
       <c r="J111" s="2"/>
@@ -7012,7 +7087,7 @@
       </c>
       <c r="F113" s="26">
         <f>F111+Ausgaben!G178</f>
-        <v>2411.8500000000249</v>
+        <v>2015.6300000000251</v>
       </c>
       <c r="G113" s="26">
         <f>G111+Ausgaben!H178</f>
@@ -7020,7 +7095,7 @@
       </c>
       <c r="H113" s="26">
         <f>H111+Ausgaben!I178</f>
-        <v>3085.7</v>
+        <v>3295.7</v>
       </c>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
@@ -7045,7 +7120,7 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27">
         <f>SUM(E113:H113)</f>
-        <v>7498.0500000000247</v>
+        <v>7311.8300000000254</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="17"/>
@@ -7785,12 +7860,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 H34:H110 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97">
+  <conditionalFormatting sqref="D6 D8:D9 D11:D14 G24:H24 E54:F58 D61:G68 D69:D77 E73:G77 A94:A97 H34:H110">
     <cfRule type="cellIs" dxfId="50" priority="67" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D22 D31 D34:D61">
+  <conditionalFormatting sqref="D20:D22 D31 D41:D61">
     <cfRule type="cellIs" dxfId="49" priority="5" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -7830,7 +7905,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E34:G40 G41:G47">
+  <conditionalFormatting sqref="G41:G47 E34:G37 G38 E39:G40">
     <cfRule type="cellIs" dxfId="41" priority="49" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -7855,63 +7930,58 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E32:H32">
+    <cfRule type="cellIs" dxfId="36" priority="1" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F25:G25">
-    <cfRule type="cellIs" dxfId="36" priority="282" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="35" priority="282" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59:G60">
-    <cfRule type="cellIs" dxfId="35" priority="24" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="24" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F72:G72">
-    <cfRule type="cellIs" dxfId="34" priority="79" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="79" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G13 A93:C93">
-    <cfRule type="cellIs" dxfId="33" priority="195" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="32" priority="195" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G26:G27">
-    <cfRule type="cellIs" dxfId="32" priority="279" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="31" priority="279" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G99 E100:G100 D110:H110 E111:H175 D115">
-    <cfRule type="cellIs" dxfId="31" priority="361" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="361" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H22">
-    <cfRule type="cellIs" dxfId="30" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28:H31 G33:H33">
-    <cfRule type="cellIs" dxfId="29" priority="56" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="56" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H10 B83">
-    <cfRule type="cellIs" dxfId="28" priority="209" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="209" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H27">
-    <cfRule type="cellIs" dxfId="27" priority="3" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H32">
-    <cfRule type="cellIs" dxfId="2" priority="2" stopIfTrue="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E32:G32">
-    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9550,14 +9620,22 @@
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="41"/>
-      <c r="B66" s="14"/>
+      <c r="B66" s="14">
+        <v>46147</v>
+      </c>
       <c r="C66" s="48">
         <v>62</v>
       </c>
-      <c r="D66" s="3"/>
-      <c r="E66" s="82"/>
+      <c r="D66" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E66" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F66" s="19"/>
-      <c r="G66" s="20"/>
+      <c r="G66" s="20">
+        <v>-47</v>
+      </c>
       <c r="H66" s="20"/>
       <c r="I66" s="20"/>
       <c r="J66" s="4"/>
@@ -9566,14 +9644,22 @@
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="41"/>
-      <c r="B67" s="14"/>
+      <c r="B67" s="14">
+        <v>46147</v>
+      </c>
       <c r="C67" s="48">
         <v>63</v>
       </c>
-      <c r="D67" s="3"/>
-      <c r="E67" s="21"/>
+      <c r="D67" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F67" s="19"/>
-      <c r="G67" s="20"/>
+      <c r="G67" s="20">
+        <v>-89</v>
+      </c>
       <c r="H67" s="20"/>
       <c r="I67" s="20"/>
       <c r="J67" s="4"/>
@@ -9582,14 +9668,22 @@
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="41"/>
-      <c r="B68" s="14"/>
+      <c r="B68" s="14">
+        <v>46147</v>
+      </c>
       <c r="C68" s="48">
         <v>64</v>
       </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="82"/>
+      <c r="D68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F68" s="16"/>
-      <c r="G68" s="20"/>
+      <c r="G68" s="20">
+        <v>-12</v>
+      </c>
       <c r="H68" s="20"/>
       <c r="I68" s="20"/>
       <c r="J68" s="4"/>
@@ -9598,14 +9692,22 @@
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="41"/>
-      <c r="B69" s="14"/>
+      <c r="B69" s="14">
+        <v>46148</v>
+      </c>
       <c r="C69" s="48">
         <v>65</v>
       </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="82"/>
+      <c r="D69" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F69" s="16"/>
-      <c r="G69" s="20"/>
+      <c r="G69" s="20">
+        <v>-83.39</v>
+      </c>
       <c r="H69" s="20"/>
       <c r="I69" s="20"/>
       <c r="J69" s="4"/>
@@ -9614,14 +9716,22 @@
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="41"/>
-      <c r="B70" s="14"/>
+      <c r="B70" s="14">
+        <v>46148</v>
+      </c>
       <c r="C70" s="48">
         <v>66</v>
       </c>
-      <c r="D70" s="81"/>
-      <c r="E70" s="82"/>
+      <c r="D70" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
+      <c r="G70" s="19">
+        <v>-5.99</v>
+      </c>
       <c r="H70" s="20"/>
       <c r="I70" s="20"/>
       <c r="J70" s="4"/>
@@ -9630,14 +9740,22 @@
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="41"/>
-      <c r="B71" s="14"/>
+      <c r="B71" s="14">
+        <v>46150</v>
+      </c>
       <c r="C71" s="48">
         <v>67</v>
       </c>
-      <c r="D71" s="81"/>
-      <c r="E71" s="82"/>
+      <c r="D71" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F71" s="19"/>
-      <c r="G71" s="20"/>
+      <c r="G71" s="20">
+        <v>-7.64</v>
+      </c>
       <c r="H71" s="20"/>
       <c r="I71" s="20"/>
       <c r="J71" s="4"/>
@@ -9646,14 +9764,22 @@
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="41"/>
-      <c r="B72" s="14"/>
+      <c r="B72" s="14">
+        <v>46157</v>
+      </c>
       <c r="C72" s="48">
         <v>68</v>
       </c>
-      <c r="D72" s="81"/>
-      <c r="E72" s="82"/>
+      <c r="D72" s="81" t="s">
+        <v>110</v>
+      </c>
+      <c r="E72" s="82" t="s">
+        <v>21</v>
+      </c>
       <c r="F72" s="19"/>
-      <c r="G72" s="20"/>
+      <c r="G72" s="20">
+        <v>-17.21</v>
+      </c>
       <c r="H72" s="20"/>
       <c r="I72" s="20"/>
       <c r="J72" s="4"/>
@@ -9662,14 +9788,22 @@
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="41"/>
-      <c r="B73" s="14"/>
+      <c r="B73" s="14">
+        <v>46160</v>
+      </c>
       <c r="C73" s="48">
         <v>69</v>
       </c>
-      <c r="D73" s="81"/>
-      <c r="E73" s="82"/>
+      <c r="D73" s="81" t="s">
+        <v>83</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F73" s="19"/>
-      <c r="G73" s="20"/>
+      <c r="G73" s="20">
+        <v>-160.59</v>
+      </c>
       <c r="H73" s="19"/>
       <c r="I73" s="20"/>
       <c r="J73" s="4"/>
@@ -9678,14 +9812,22 @@
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="41"/>
-      <c r="B74" s="14"/>
+      <c r="B74" s="14">
+        <v>46161</v>
+      </c>
       <c r="C74" s="48">
         <v>70</v>
       </c>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
+      <c r="D74" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="F74" s="19"/>
-      <c r="G74" s="20"/>
+      <c r="G74" s="20">
+        <v>-3.4</v>
+      </c>
       <c r="H74" s="20"/>
       <c r="I74" s="20"/>
       <c r="J74" s="4"/>
@@ -9694,16 +9836,24 @@
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="41"/>
-      <c r="B75" s="14"/>
+      <c r="B75" s="14">
+        <v>46161</v>
+      </c>
       <c r="C75" s="48">
         <v>71</v>
       </c>
-      <c r="D75" s="3"/>
-      <c r="E75" s="82"/>
+      <c r="D75" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="F75" s="19"/>
       <c r="G75" s="20"/>
       <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
+      <c r="I75" s="20">
+        <v>-10.5</v>
+      </c>
       <c r="J75" s="4"/>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
@@ -11354,7 +11504,7 @@
       </c>
       <c r="G178" s="32">
         <f>SUM(G3:G177)</f>
-        <v>-3504.5299999999988</v>
+        <v>-3930.7499999999986</v>
       </c>
       <c r="H178" s="32">
         <f>SUM(H3:H177)</f>
@@ -11362,7 +11512,7 @@
       </c>
       <c r="I178" s="32">
         <f>SUM(I3:I177)</f>
-        <v>-3195.91</v>
+        <v>-3206.41</v>
       </c>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
@@ -12275,128 +12425,138 @@
   <mergeCells count="1">
     <mergeCell ref="B1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A3:A242 E33 E66:E73 E133:E144 E75:E123">
-    <cfRule type="cellIs" dxfId="26" priority="488" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="A3:A242 E33 E76:E123 E133:E144">
+    <cfRule type="cellIs" dxfId="25" priority="490" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B129:B142">
-    <cfRule type="cellIs" dxfId="25" priority="471" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="473" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B156:B244">
-    <cfRule type="cellIs" dxfId="24" priority="28" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="30" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C155 C157 C159 C161 C163 C165 C167 C173 C175">
-    <cfRule type="cellIs" dxfId="23" priority="29" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="31" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177:C243 J179 I179:I244">
-    <cfRule type="cellIs" dxfId="22" priority="718" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="720" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D132">
-    <cfRule type="cellIs" dxfId="21" priority="486" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="488" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D149">
-    <cfRule type="cellIs" dxfId="20" priority="73" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="75" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D153:D154">
-    <cfRule type="cellIs" dxfId="19" priority="457" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="459" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D158:D163">
-    <cfRule type="cellIs" dxfId="18" priority="14" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="16" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D164:E165 D166:D167 C169:D169 D170:E170 C171:D171">
-    <cfRule type="cellIs" dxfId="17" priority="21" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="23" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D177:E179">
-    <cfRule type="cellIs" dxfId="16" priority="23" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="25" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D179:H242">
-    <cfRule type="cellIs" dxfId="15" priority="670" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="672" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E4 E7:E8 E11 E13 E15 E23 E125:E131 E146:E163">
-    <cfRule type="cellIs" dxfId="14" priority="9" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19:E20">
-    <cfRule type="cellIs" dxfId="13" priority="5" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="7" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E35:E37">
-    <cfRule type="cellIs" dxfId="12" priority="6" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="8" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E42">
-    <cfRule type="cellIs" dxfId="11" priority="4" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="6" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58:E59">
-    <cfRule type="cellIs" dxfId="10" priority="3" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="5" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61">
+    <cfRule type="cellIs" dxfId="8" priority="4" stopIfTrue="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E64">
+    <cfRule type="cellIs" dxfId="7" priority="3" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E169">
-    <cfRule type="cellIs" dxfId="9" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="13" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171:E176">
-    <cfRule type="cellIs" dxfId="8" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="12" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F69">
-    <cfRule type="cellIs" dxfId="6" priority="8" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F98:F99">
-    <cfRule type="cellIs" dxfId="5" priority="131" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="133" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="cellIs" dxfId="4" priority="15" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E61">
-    <cfRule type="cellIs" dxfId="3" priority="2" stopIfTrue="1" operator="lessThan">
+  <conditionalFormatting sqref="E66:E68">
+    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E64">
+  <conditionalFormatting sqref="E72">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E146:E177 E125:E131 E133:E144 E58:E59 E75:E123 E61 E64 E66:E73" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E42 E19:E20 E35:E37 E33 E23 E15 E13 E11 E7:E8 E3:E4 E146:E177 E125:E131 E133:E144 E58:E59 E72 E61 E64 E66:E68 E76:E123" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>$L$1:$L$19</formula1>
     </dataValidation>
   </dataValidations>
